--- a/Additional document/templateAddSoldier.xlsx
+++ b/Additional document/templateAddSoldier.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="560">
   <si>
     <t>soldierId</t>
   </si>
@@ -41,7 +41,7 @@
     <t>99901 Richard</t>
   </si>
   <si>
-    <t>Swedes</t>
+    <t>Sweden</t>
   </si>
   <si>
     <t>99903 Hakan</t>
@@ -1635,9 +1635,6 @@
   </si>
   <si>
     <t>12310 THEODORE</t>
-  </si>
-  <si>
-    <t>14701 JOHAN</t>
   </si>
   <si>
     <t>99941 Maria Hjortstorp</t>
@@ -1722,7 +1719,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1733,6 +1730,44 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1887,12 +1922,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2252,144 +2293,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2402,10 +2444,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="35" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="35" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="35" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2460,7 +2588,17 @@
     <cellStyle name="Normal 2" xfId="49"/>
     <cellStyle name="Normal 5" xfId="50"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2824,5824 +2962,6352 @@
     <col min="2" max="2" width="28.2727272727273" style="2" customWidth="1"/>
     <col min="3" max="3" width="25" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="33.9090909090909" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="6">
+    <row r="2" spans="1:5">
+      <c r="A2" s="7">
         <v>99901</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="6">
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7">
         <v>99903</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="6">
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7">
         <v>99905</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="6">
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7">
         <v>99907</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="6">
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7">
         <v>99909</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="6">
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7">
         <v>99911</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="6">
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7">
         <v>99913</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="6">
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7">
         <v>99914</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="6">
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7">
         <v>99915</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="6">
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7">
         <v>99917</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="6">
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7">
         <v>99919</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="6">
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="7">
         <v>99920</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="6">
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7">
         <v>99918</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="6">
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7">
         <v>99916</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="6">
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="7">
         <v>99912</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="6">
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7">
         <v>99910</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="6">
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7">
         <v>99908</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="6">
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7">
         <v>99906</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="6">
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7">
         <v>99904</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="6">
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7">
         <v>99902</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="6">
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7">
         <v>99921</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="6">
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7">
         <v>99923</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="6">
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7">
         <v>99932</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="6">
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7">
         <v>99933</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="6">
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7">
         <v>99936</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="6">
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7">
         <v>99937</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="6">
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7">
         <v>99934</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="6">
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7">
         <v>99935</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="6">
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7">
         <v>99930</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="6">
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7">
         <v>99931</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="6">
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7">
         <v>99922</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="6">
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7">
         <v>10002</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="6">
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7">
         <v>12101</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="6">
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7">
         <v>12102</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="6">
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7">
         <v>12201</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="6">
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7">
         <v>12202</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="6">
+      <c r="E37" s="10"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7">
         <v>12107</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="6">
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7">
         <v>12108</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="6">
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7">
         <v>12109</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="6">
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7">
         <v>12110</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="6">
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7">
         <v>12203</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="6">
+      <c r="E42" s="9"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7">
         <v>12205</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="6">
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7">
         <v>12210</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="6">
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7">
         <v>12206</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="6">
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7">
         <v>12303</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="6">
+      <c r="E46" s="10"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7">
         <v>12305</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="6">
+      <c r="E47" s="10"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7">
         <v>12301</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="6">
+      <c r="E48" s="10"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7">
         <v>12302</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="6">
+      <c r="E49" s="10"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7">
         <v>12304</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="6">
+      <c r="E50" s="10"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7">
         <v>12307</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="6">
+      <c r="E51" s="12"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7">
         <v>12001</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="6">
+      <c r="E52" s="8"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7">
         <v>12002</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="6">
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7">
         <v>12309</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="6">
+      <c r="E54" s="10"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7">
         <v>12306</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="6">
+      <c r="E55" s="10"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7">
         <v>12308</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="6">
+      <c r="E56" s="10"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7">
         <v>12208</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="6">
+      <c r="E57" s="10"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7">
         <v>12209</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>60</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="6">
+      <c r="E58" s="11"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7">
         <v>12204</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="6">
+      <c r="E59" s="10"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7">
         <v>12207</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="6">
+      <c r="E60" s="10"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7">
         <v>12111</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="6">
+      <c r="E61" s="10"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7">
         <v>12106</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>64</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="6">
+      <c r="E62" s="10"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7">
         <v>12103</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="6">
+      <c r="E63" s="11"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7">
         <v>12104</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>66</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="6">
+      <c r="E64" s="12"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7">
         <v>12105</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="6">
+      <c r="E65" s="10"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7">
         <v>10003</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="6">
+      <c r="E66" s="8"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7">
         <v>10048</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="6">
+      <c r="E67" s="11"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7">
         <v>13101</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="6">
+      <c r="E68" s="11"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7">
         <v>13102</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="6">
+      <c r="E69" s="11"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7">
         <v>13210</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="7" t="s">
         <v>72</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="6">
+      <c r="E70" s="10"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7">
         <v>13105</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>73</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="6">
+      <c r="E71" s="10"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7">
         <v>13108</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="6">
+      <c r="E72" s="9"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7">
         <v>13109</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="6">
+      <c r="E73" s="10"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7">
         <v>13204</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="7" t="s">
         <v>76</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="6">
+      <c r="E74" s="11"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7">
         <v>13207</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="6">
+      <c r="E75" s="10"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7">
         <v>13208</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="7" t="s">
         <v>78</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="6">
+      <c r="E76" s="10"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7">
         <v>13209</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="6">
+      <c r="E77" s="10"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7">
         <v>13103</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="6">
+      <c r="E78" s="11"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7">
         <v>13301</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="6">
+      <c r="E79" s="11"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7">
         <v>13302</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="6">
+      <c r="E80" s="11"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7">
         <v>13304</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="6">
+      <c r="E81" s="8"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7">
         <v>13307</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="7" t="s">
         <v>84</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="6">
+      <c r="E82" s="11"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7">
         <v>13310</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="6">
+      <c r="E83" s="10"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7">
         <v>13306</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="7" t="s">
         <v>86</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="6">
+      <c r="E84" s="10"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7">
         <v>13001</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="6">
+      <c r="E85" s="11"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7">
         <v>13002</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="6">
+      <c r="E86" s="11"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7">
         <v>13308</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="6">
+      <c r="E87" s="9"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="7">
         <v>13309</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="6">
+      <c r="E88" s="11"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="7">
         <v>13303</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="6">
+      <c r="E89" s="11"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="7">
         <v>13305</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="6">
+      <c r="E90" s="11"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="7">
         <v>13203</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="6">
+      <c r="E91" s="11"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="7">
         <v>13205</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="6">
+      <c r="E92" s="11"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="7">
         <v>13201</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="6">
+      <c r="E93" s="11"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="7">
         <v>13202</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="6">
+      <c r="E94" s="11"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="7">
         <v>13110</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="6">
+      <c r="E95" s="10"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="7">
         <v>13111</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="7" t="s">
         <v>98</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="6">
+      <c r="E96" s="11"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="7">
         <v>13107</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="6">
+      <c r="E97" s="11"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="7">
         <v>13106</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="6">
+      <c r="E98" s="13"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="7">
         <v>13104</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="7" t="s">
         <v>101</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="6">
+      <c r="E99" s="10"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="7">
         <v>13206</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="6">
+      <c r="E100" s="10"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="7">
         <v>10041</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="6">
+      <c r="E101" s="11"/>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="7">
         <v>20001</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="6">
+      <c r="E102" s="14"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="7">
         <v>20002</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="6">
+      <c r="E103" s="14"/>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="7">
         <v>20003</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="6">
+      <c r="E104" s="15"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="7">
         <v>20041</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="6">
+      <c r="E105" s="16"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="7">
         <v>21101</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="7" t="s">
         <v>108</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="6">
+      <c r="E106" s="16"/>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="7">
         <v>21102</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="6">
+      <c r="E107" s="16"/>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="7">
         <v>21103</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="7" t="s">
         <v>110</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="6">
+      <c r="E108" s="16"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="7">
         <v>21203</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="6">
+      <c r="E109" s="16"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="7">
         <v>21105</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="6">
+      <c r="E110" s="15"/>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="7">
         <v>21104</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="7" t="s">
         <v>113</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="6">
+      <c r="E111" s="16"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="7">
         <v>21107</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="7" t="s">
         <v>114</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="6">
+      <c r="E112" s="15"/>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="7">
         <v>21108</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="6">
+      <c r="E113" s="16"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="7">
         <v>21109</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="7" t="s">
         <v>116</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="6">
+      <c r="E114" s="16"/>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="7">
         <v>21106</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="7" t="s">
         <v>117</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="6">
+      <c r="E115" s="16"/>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="7">
         <v>21201</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="6">
+      <c r="E116" s="16"/>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="7">
         <v>21202</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="7" t="s">
         <v>119</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="6">
+      <c r="E117" s="16"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="7">
         <v>21205</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="6">
+      <c r="E118" s="16"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="7">
         <v>21204</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="7" t="s">
         <v>121</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="6">
+      <c r="E119" s="16"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="7">
         <v>21207</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="7" t="s">
         <v>122</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="6">
+      <c r="E120" s="16"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="7">
         <v>21208</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="7" t="s">
         <v>123</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="6">
+      <c r="E121" s="16"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="7">
         <v>21209</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="7" t="s">
         <v>124</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="6">
+      <c r="E122" s="16"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="7">
         <v>21206</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="7" t="s">
         <v>125</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="6">
+      <c r="E123" s="16"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="7">
         <v>21301</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="7" t="s">
         <v>126</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="6">
+      <c r="E124" s="16"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="7">
         <v>21302</v>
       </c>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="7" t="s">
         <v>127</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="6">
+      <c r="E125" s="16"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="7">
         <v>21305</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B126" s="7" t="s">
         <v>128</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="6">
+      <c r="E126" s="15"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="7">
         <v>21304</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B127" s="7" t="s">
         <v>129</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="6">
+      <c r="E127" s="16"/>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="7">
         <v>21307</v>
       </c>
-      <c r="B128" s="6" t="s">
+      <c r="B128" s="7" t="s">
         <v>130</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="6">
+      <c r="E128" s="16"/>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="7">
         <v>21308</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="6">
+      <c r="E129" s="16"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="7">
         <v>21309</v>
       </c>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="7" t="s">
         <v>132</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="6">
+      <c r="E130" s="15"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="7">
         <v>21306</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B131" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="6">
+      <c r="E131" s="16"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="7">
         <v>21001</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="7" t="s">
         <v>134</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="6">
+      <c r="E132" s="16"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="7">
         <v>21002</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="6">
+      <c r="E133" s="16"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="7">
         <v>20048</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="7" t="s">
         <v>136</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" s="6">
+      <c r="E134" s="16"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="7">
         <v>22001</v>
       </c>
-      <c r="B135" s="6" t="s">
+      <c r="B135" s="7" t="s">
         <v>137</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="6">
+      <c r="E135" s="17"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="7">
         <v>22002</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="6">
+      <c r="E136" s="17"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="7">
         <v>22101</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="7" t="s">
         <v>139</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="6">
+      <c r="E137" s="17"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="7">
         <v>22102</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="7" t="s">
         <v>140</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" s="6">
+      <c r="E138" s="17"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="7">
         <v>22105</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B139" s="7" t="s">
         <v>141</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="6">
+      <c r="E139" s="17"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="7">
         <v>22104</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="7" t="s">
         <v>142</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="6">
+      <c r="E140" s="17"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="7">
         <v>22107</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="7" t="s">
         <v>143</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" s="6">
+      <c r="E141" s="17"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="7">
         <v>22110</v>
       </c>
-      <c r="B142" s="6" t="s">
+      <c r="B142" s="7" t="s">
         <v>144</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="6">
+      <c r="E142" s="17"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="7">
         <v>22109</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="7" t="s">
         <v>145</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="6">
+      <c r="E143" s="17"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7">
         <v>22108</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B144" s="7" t="s">
         <v>146</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" s="6">
+      <c r="E144" s="17"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="7">
         <v>22201</v>
       </c>
-      <c r="B145" s="6" t="s">
+      <c r="B145" s="7" t="s">
         <v>147</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="6">
+      <c r="E145" s="17"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="7">
         <v>22208</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B146" s="7" t="s">
         <v>148</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" s="6">
+      <c r="E146" s="17"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="7">
         <v>22205</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B147" s="7" t="s">
         <v>149</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" s="6">
+      <c r="E147" s="17"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="7">
         <v>22204</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B148" s="7" t="s">
         <v>150</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" s="6">
+      <c r="E148" s="17"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="7">
         <v>22202</v>
       </c>
-      <c r="B149" s="6" t="s">
+      <c r="B149" s="7" t="s">
         <v>151</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" s="6">
+      <c r="E149" s="17"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="7">
         <v>22210</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B150" s="7" t="s">
         <v>152</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" s="6">
+      <c r="E150" s="17"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="7">
         <v>22209</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B151" s="7" t="s">
         <v>153</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" s="6">
+      <c r="E151" s="17"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="7">
         <v>22207</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B152" s="7" t="s">
         <v>154</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" s="6">
+      <c r="E152" s="17"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="7">
         <v>22301</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B153" s="7" t="s">
         <v>155</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" s="6">
+      <c r="E153" s="17"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="7">
         <v>22302</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B154" s="7" t="s">
         <v>156</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" s="6">
+      <c r="E154" s="17"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="7">
         <v>22305</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B155" s="7" t="s">
         <v>157</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E155" s="17"/>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="6">
+      <c r="A156" s="7">
         <v>22304</v>
       </c>
-      <c r="B156" s="6" t="s">
+      <c r="B156" s="7" t="s">
         <v>158</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F156" s="7"/>
+      <c r="E156" s="17"/>
+      <c r="F156" s="18"/>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="6">
+      <c r="A157" s="7">
         <v>22310</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B157" s="7" t="s">
         <v>159</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F157" s="7"/>
+      <c r="E157" s="17"/>
+      <c r="F157" s="18"/>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="6">
+      <c r="A158" s="7">
         <v>22307</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B158" s="7" t="s">
         <v>160</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F158" s="7"/>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="6">
+      <c r="E158" s="17"/>
+      <c r="F158" s="18"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="7">
         <v>22309</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B159" s="7" t="s">
         <v>161</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" s="6">
+      <c r="E159" s="17"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="7">
         <v>22308</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B160" s="7" t="s">
         <v>162</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" s="6">
+      <c r="E160" s="17"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="7">
         <v>22103</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B161" s="7" t="s">
         <v>163</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="6">
+      <c r="E161" s="17"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="7">
         <v>23105</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B162" s="7" t="s">
         <v>164</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" s="6">
+      <c r="E162" s="19"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="7">
         <v>23104</v>
       </c>
-      <c r="B163" s="6" t="s">
+      <c r="B163" s="7" t="s">
         <v>165</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="6">
+      <c r="E163" s="19"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="7">
         <v>23103</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B164" s="7" t="s">
         <v>166</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="6">
+      <c r="E164" s="19"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="7">
         <v>23101</v>
       </c>
-      <c r="B165" s="6" t="s">
+      <c r="B165" s="7" t="s">
         <v>167</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="6">
+      <c r="E165" s="16"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="7">
         <v>23102</v>
       </c>
-      <c r="B166" s="6" t="s">
+      <c r="B166" s="7" t="s">
         <v>168</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="6">
+      <c r="E166" s="16"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="7">
         <v>23107</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B167" s="7" t="s">
         <v>169</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" s="6">
+      <c r="E167" s="17"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="7">
         <v>23108</v>
       </c>
-      <c r="B168" s="6" t="s">
+      <c r="B168" s="7" t="s">
         <v>170</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="6">
+      <c r="E168" s="17"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="7">
         <v>23002</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B169" s="7" t="s">
         <v>171</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="6">
+      <c r="E169" s="17"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="7">
         <v>23001</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B170" s="7" t="s">
         <v>172</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" s="6">
+      <c r="E170" s="17"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="7">
         <v>52303</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B171" s="7" t="s">
         <v>173</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="6">
+      <c r="E171" s="17"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="7">
         <v>52103</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="7" t="s">
         <v>174</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" s="6">
+      <c r="E172" s="17"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="7">
         <v>52313</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B173" s="7" t="s">
         <v>175</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" s="6">
+      <c r="E173" s="17"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="7">
         <v>52312</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B174" s="7" t="s">
         <v>176</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" s="6">
+      <c r="E174" s="17"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="7">
         <v>52308</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B175" s="7" t="s">
         <v>177</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" s="6">
+      <c r="E175" s="17"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="7">
         <v>52310</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B176" s="7" t="s">
         <v>178</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="6">
+      <c r="E176" s="17"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="7">
         <v>52311</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B177" s="7" t="s">
         <v>179</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" s="6">
+      <c r="E177" s="17"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="7">
         <v>52105</v>
       </c>
-      <c r="B178" s="6" t="s">
+      <c r="B178" s="7" t="s">
         <v>180</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" s="6">
+      <c r="E178" s="17"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="7">
         <v>52309</v>
       </c>
-      <c r="B179" s="6" t="s">
+      <c r="B179" s="7" t="s">
         <v>181</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" s="6">
+      <c r="E179" s="17"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="7">
         <v>52307</v>
       </c>
-      <c r="B180" s="6" t="s">
+      <c r="B180" s="7" t="s">
         <v>182</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181" s="6">
+      <c r="E180" s="17"/>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="7">
         <v>52104</v>
       </c>
-      <c r="B181" s="6" t="s">
+      <c r="B181" s="7" t="s">
         <v>183</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="6">
+      <c r="E181" s="17"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="7">
         <v>52205</v>
       </c>
-      <c r="B182" s="6" t="s">
+      <c r="B182" s="7" t="s">
         <v>184</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" s="6">
+      <c r="E182" s="17"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="7">
         <v>52203</v>
       </c>
-      <c r="B183" s="6" t="s">
+      <c r="B183" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="6">
+      <c r="E183" s="17"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="7">
         <v>52204</v>
       </c>
-      <c r="B184" s="6" t="s">
+      <c r="B184" s="7" t="s">
         <v>186</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" s="6">
+      <c r="E184" s="17"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="7">
         <v>52401</v>
       </c>
-      <c r="B185" s="6" t="s">
+      <c r="B185" s="7" t="s">
         <v>187</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="6">
+      <c r="E185" s="17"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="7">
         <v>52415</v>
       </c>
-      <c r="B186" s="6" t="s">
+      <c r="B186" s="7" t="s">
         <v>188</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" s="6">
+      <c r="E186" s="17"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="7">
         <v>52455</v>
       </c>
-      <c r="B187" s="6" t="s">
+      <c r="B187" s="7" t="s">
         <v>189</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" s="6">
+      <c r="E187" s="20"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="7">
         <v>52445</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B188" s="7" t="s">
         <v>190</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" s="6">
+      <c r="E188" s="20"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="7">
         <v>52402</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B189" s="7" t="s">
         <v>191</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" s="6">
+      <c r="E189" s="20"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="7">
         <v>52405</v>
       </c>
-      <c r="B190" s="6" t="s">
+      <c r="B190" s="7" t="s">
         <v>192</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" s="6">
+      <c r="E190" s="20"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="7">
         <v>52425</v>
       </c>
-      <c r="B191" s="6" t="s">
+      <c r="B191" s="7" t="s">
         <v>193</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="6">
+      <c r="E191" s="21"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="7">
         <v>52435</v>
       </c>
-      <c r="B192" s="6" t="s">
+      <c r="B192" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" s="6">
+      <c r="E192" s="21"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="7">
         <v>52501</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B193" s="7" t="s">
         <v>195</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" s="6">
+      <c r="E193" s="21"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="7">
         <v>52508</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B194" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" s="6">
+      <c r="E194" s="20"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="7">
         <v>52507</v>
       </c>
-      <c r="B195" s="6" t="s">
+      <c r="B195" s="7" t="s">
         <v>197</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" s="6">
+      <c r="E195" s="20"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="7">
         <v>52509</v>
       </c>
-      <c r="B196" s="6" t="s">
+      <c r="B196" s="7" t="s">
         <v>198</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" s="6">
+      <c r="E196" s="20"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="7">
         <v>52601</v>
       </c>
-      <c r="B197" s="6" t="s">
+      <c r="B197" s="7" t="s">
         <v>199</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" s="6">
+      <c r="E197" s="20"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="7">
         <v>52607</v>
       </c>
-      <c r="B198" s="6" t="s">
+      <c r="B198" s="7" t="s">
         <v>200</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" s="6" t="s">
+      <c r="E198" s="20"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="B199" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" s="6" t="s">
+      <c r="E199" s="17"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B200" s="6" t="s">
+      <c r="B200" s="7" t="s">
         <v>204</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" s="6" t="s">
+      <c r="E200" s="17"/>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B201" s="6" t="s">
+      <c r="B201" s="7" t="s">
         <v>206</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" s="6" t="s">
+      <c r="E201" s="17"/>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B202" s="6" t="s">
+      <c r="B202" s="7" t="s">
         <v>208</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" s="6" t="s">
+      <c r="E202" s="17"/>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B203" s="6" t="s">
+      <c r="B203" s="7" t="s">
         <v>210</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" s="6" t="s">
+      <c r="E203" s="17"/>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B204" s="6" t="s">
+      <c r="B204" s="7" t="s">
         <v>212</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" s="6" t="s">
+      <c r="E204" s="17"/>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B205" s="6" t="s">
+      <c r="B205" s="7" t="s">
         <v>214</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="6" t="s">
+      <c r="E205" s="17"/>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="B206" s="7" t="s">
         <v>216</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" s="6">
+      <c r="E206" s="17"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="7">
         <v>52002</v>
       </c>
-      <c r="B207" s="6" t="s">
+      <c r="B207" s="7" t="s">
         <v>217</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" s="6">
+      <c r="E207" s="17"/>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="7">
         <v>52001</v>
       </c>
-      <c r="B208" s="6" t="s">
+      <c r="B208" s="7" t="s">
         <v>218</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" s="6">
+      <c r="E208" s="17"/>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="7">
         <v>53001</v>
       </c>
-      <c r="B209" s="6" t="s">
+      <c r="B209" s="7" t="s">
         <v>219</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210" s="6">
+      <c r="E209" s="17"/>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="7">
         <v>53201</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="B210" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211" s="6">
+      <c r="E210" s="17"/>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="7">
         <v>53501</v>
       </c>
-      <c r="B211" s="6" t="s">
+      <c r="B211" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212" s="6">
+      <c r="E211" s="17"/>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="7">
         <v>53312</v>
       </c>
-      <c r="B212" s="6" t="s">
+      <c r="B212" s="7" t="s">
         <v>222</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="6">
+      <c r="E212" s="17"/>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="7">
         <v>53207</v>
       </c>
-      <c r="B213" s="6" t="s">
+      <c r="B213" s="7" t="s">
         <v>223</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="6">
+      <c r="E213" s="17"/>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="7">
         <v>53507</v>
       </c>
-      <c r="B214" s="6" t="s">
+      <c r="B214" s="7" t="s">
         <v>224</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="215" spans="1:3">
-      <c r="A215" s="6">
+      <c r="E214" s="17"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="7">
         <v>53509</v>
       </c>
-      <c r="B215" s="6" t="s">
+      <c r="B215" s="7" t="s">
         <v>225</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="216" spans="1:3">
-      <c r="A216" s="6">
+      <c r="E215" s="17"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="7">
         <v>53508</v>
       </c>
-      <c r="B216" s="6" t="s">
+      <c r="B216" s="7" t="s">
         <v>226</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="6">
+      <c r="E216" s="17"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="7">
         <v>53209</v>
       </c>
-      <c r="B217" s="6" t="s">
+      <c r="B217" s="7" t="s">
         <v>227</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="6">
+      <c r="E217" s="17"/>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="7">
         <v>53502</v>
       </c>
-      <c r="B218" s="6" t="s">
+      <c r="B218" s="7" t="s">
         <v>228</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="6">
+      <c r="E218" s="17"/>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="7">
         <v>53307</v>
       </c>
-      <c r="B219" s="6" t="s">
+      <c r="B219" s="7" t="s">
         <v>229</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="220" spans="1:3">
-      <c r="A220" s="6">
+      <c r="E219" s="17"/>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="7">
         <v>53408</v>
       </c>
-      <c r="B220" s="6" t="s">
+      <c r="B220" s="7" t="s">
         <v>230</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="6">
+      <c r="E220" s="17"/>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="7">
         <v>53313</v>
       </c>
-      <c r="B221" s="6" t="s">
+      <c r="B221" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222" s="6">
+      <c r="E221" s="17"/>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="7">
         <v>53107</v>
       </c>
-      <c r="B222" s="6" t="s">
+      <c r="B222" s="7" t="s">
         <v>232</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="6">
+      <c r="E222" s="17"/>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="7">
         <v>53407</v>
       </c>
-      <c r="B223" s="6" t="s">
+      <c r="B223" s="7" t="s">
         <v>233</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="6">
+      <c r="E223" s="17"/>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="7">
         <v>52801</v>
       </c>
-      <c r="B224" s="6" t="s">
+      <c r="B224" s="7" t="s">
         <v>234</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="225" spans="1:3">
-      <c r="A225" s="6">
+      <c r="E224" s="21"/>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="7">
         <v>53409</v>
       </c>
-      <c r="B225" s="6" t="s">
+      <c r="B225" s="7" t="s">
         <v>235</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="6">
+      <c r="E225" s="22"/>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="7">
         <v>53310</v>
       </c>
-      <c r="B226" s="6" t="s">
+      <c r="B226" s="7" t="s">
         <v>236</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="6">
+      <c r="E226" s="17"/>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="7">
         <v>53308</v>
       </c>
-      <c r="B227" s="6" t="s">
+      <c r="B227" s="7" t="s">
         <v>237</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="6">
+      <c r="E227" s="17"/>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="7">
         <v>53208</v>
       </c>
-      <c r="B228" s="6" t="s">
+      <c r="B228" s="7" t="s">
         <v>238</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="6">
+      <c r="E228" s="17"/>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="7">
         <v>53102</v>
       </c>
-      <c r="B229" s="6" t="s">
+      <c r="B229" s="7" t="s">
         <v>239</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="6">
+      <c r="E229" s="17"/>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="7">
         <v>53108</v>
       </c>
-      <c r="B230" s="6" t="s">
+      <c r="B230" s="7" t="s">
         <v>240</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="6">
+      <c r="E230" s="17"/>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="7">
         <v>53101</v>
       </c>
-      <c r="B231" s="6" t="s">
+      <c r="B231" s="7" t="s">
         <v>241</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="6">
+      <c r="E231" s="17"/>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="7">
         <v>53302</v>
       </c>
-      <c r="B232" s="6" t="s">
+      <c r="B232" s="7" t="s">
         <v>242</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="6">
+      <c r="E232" s="17"/>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="7">
         <v>53301</v>
       </c>
-      <c r="B233" s="6" t="s">
+      <c r="B233" s="7" t="s">
         <v>243</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234" s="6">
+      <c r="E233" s="23"/>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="7">
         <v>53311</v>
       </c>
-      <c r="B234" s="6" t="s">
+      <c r="B234" s="7" t="s">
         <v>244</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235" s="6">
+      <c r="E234" s="23"/>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="7">
         <v>53401</v>
       </c>
-      <c r="B235" s="6" t="s">
+      <c r="B235" s="7" t="s">
         <v>245</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="6">
+      <c r="E235" s="17"/>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="7">
         <v>53002</v>
       </c>
-      <c r="B236" s="6" t="s">
+      <c r="B236" s="7" t="s">
         <v>246</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" s="6" t="s">
+      <c r="E236" s="24"/>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B237" s="6" t="s">
+      <c r="B237" s="7" t="s">
         <v>248</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="6" t="s">
+      <c r="E237" s="25"/>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B238" s="6" t="s">
+      <c r="B238" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="6" t="s">
+      <c r="E238" s="25"/>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B239" s="6" t="s">
+      <c r="B239" s="7" t="s">
         <v>252</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="6" t="s">
+      <c r="E239" s="25"/>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B240" s="6" t="s">
+      <c r="B240" s="7" t="s">
         <v>254</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="6" t="s">
+      <c r="E240" s="25"/>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B241" s="6" t="s">
+      <c r="B241" s="7" t="s">
         <v>256</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" s="6" t="s">
+      <c r="E241" s="25"/>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B242" s="6" t="s">
+      <c r="B242" s="7" t="s">
         <v>258</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243" s="6" t="s">
+      <c r="E242" s="25"/>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B243" s="6" t="s">
+      <c r="B243" s="7" t="s">
         <v>260</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244" s="6" t="s">
+      <c r="E243" s="25"/>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B244" s="6" t="s">
+      <c r="B244" s="7" t="s">
         <v>262</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" s="6" t="s">
+      <c r="E244" s="25"/>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B245" s="6" t="s">
+      <c r="B245" s="7" t="s">
         <v>264</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" s="6" t="s">
+      <c r="E245" s="25"/>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B246" s="6" t="s">
+      <c r="B246" s="7" t="s">
         <v>266</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="6" t="s">
+      <c r="E246" s="25"/>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B247" s="6" t="s">
+      <c r="B247" s="7" t="s">
         <v>268</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" s="6" t="s">
+      <c r="E247" s="25"/>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B248" s="6" t="s">
+      <c r="B248" s="7" t="s">
         <v>270</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" s="6">
+      <c r="E248" s="25"/>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="7">
         <v>51401</v>
       </c>
-      <c r="B249" s="6" t="s">
+      <c r="B249" s="7" t="s">
         <v>271</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" s="6">
+      <c r="E249" s="16"/>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="7">
         <v>51203</v>
       </c>
-      <c r="B250" s="6" t="s">
+      <c r="B250" s="7" t="s">
         <v>272</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" s="6">
+      <c r="E250" s="16"/>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="7">
         <v>51407</v>
       </c>
-      <c r="B251" s="6" t="s">
+      <c r="B251" s="7" t="s">
         <v>273</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252" s="6">
+      <c r="E251" s="16"/>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="7">
         <v>51501</v>
       </c>
-      <c r="B252" s="6" t="s">
+      <c r="B252" s="7" t="s">
         <v>274</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" s="6">
+      <c r="E252" s="16"/>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="7">
         <v>51105</v>
       </c>
-      <c r="B253" s="6" t="s">
+      <c r="B253" s="7" t="s">
         <v>275</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254" s="6">
+      <c r="E253" s="16"/>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="7">
         <v>51108</v>
       </c>
-      <c r="B254" s="6" t="s">
+      <c r="B254" s="7" t="s">
         <v>276</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="255" spans="1:3">
-      <c r="A255" s="6">
+      <c r="E254" s="16"/>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="7">
         <v>51305</v>
       </c>
-      <c r="B255" s="6" t="s">
+      <c r="B255" s="7" t="s">
         <v>277</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256" s="6">
+      <c r="E255" s="16"/>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="7">
         <v>51207</v>
       </c>
-      <c r="B256" s="6" t="s">
+      <c r="B256" s="7" t="s">
         <v>278</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257" s="6">
+      <c r="E256" s="16"/>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="7">
         <v>51307</v>
       </c>
-      <c r="B257" s="6" t="s">
+      <c r="B257" s="7" t="s">
         <v>279</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" s="6">
+      <c r="E257" s="16"/>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="7">
         <v>51308</v>
       </c>
-      <c r="B258" s="6" t="s">
+      <c r="B258" s="7" t="s">
         <v>280</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" s="6">
+      <c r="E258" s="16"/>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="7">
         <v>51001</v>
       </c>
-      <c r="B259" s="6" t="s">
+      <c r="B259" s="7" t="s">
         <v>281</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" s="6">
+      <c r="E259" s="16"/>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="7">
         <v>51002</v>
       </c>
-      <c r="B260" s="6" t="s">
+      <c r="B260" s="7" t="s">
         <v>282</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="261" spans="1:3">
-      <c r="A261" s="6">
+      <c r="E260" s="16"/>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="7">
         <v>51205</v>
       </c>
-      <c r="B261" s="6" t="s">
+      <c r="B261" s="7" t="s">
         <v>283</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="262" spans="1:3">
-      <c r="A262" s="6">
+      <c r="E261" s="16"/>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="7">
         <v>51208</v>
       </c>
-      <c r="B262" s="6" t="s">
+      <c r="B262" s="7" t="s">
         <v>284</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="263" spans="1:3">
-      <c r="A263" s="6">
+      <c r="E262" s="16"/>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="7">
         <v>51303</v>
       </c>
-      <c r="B263" s="6" t="s">
+      <c r="B263" s="7" t="s">
         <v>285</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="264" spans="1:3">
-      <c r="A264" s="6">
+      <c r="E263" s="16"/>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="7">
         <v>51107</v>
       </c>
-      <c r="B264" s="6" t="s">
+      <c r="B264" s="7" t="s">
         <v>286</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="265" spans="1:3">
-      <c r="A265" s="6">
+      <c r="E264" s="16"/>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="7">
         <v>51103</v>
       </c>
-      <c r="B265" s="6" t="s">
+      <c r="B265" s="7" t="s">
         <v>287</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="266" spans="1:3">
-      <c r="A266" s="6">
+      <c r="E265" s="16"/>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="7">
         <v>51505</v>
       </c>
-      <c r="B266" s="6" t="s">
+      <c r="B266" s="7" t="s">
         <v>288</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="267" spans="1:3">
-      <c r="A267" s="6">
+      <c r="E266" s="16"/>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="7">
         <v>51515</v>
       </c>
-      <c r="B267" s="6" t="s">
+      <c r="B267" s="7" t="s">
         <v>289</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="268" spans="1:3">
-      <c r="A268" s="6">
+      <c r="E267" s="16"/>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="7">
         <v>51405</v>
       </c>
-      <c r="B268" s="6" t="s">
+      <c r="B268" s="7" t="s">
         <v>290</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="269" spans="1:3">
-      <c r="A269" s="6">
+      <c r="E268" s="16"/>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="7">
         <v>51408</v>
       </c>
-      <c r="B269" s="6" t="s">
+      <c r="B269" s="7" t="s">
         <v>291</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" s="6">
+      <c r="E269" s="16"/>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="7">
         <v>55001</v>
       </c>
-      <c r="B270" s="6" t="s">
+      <c r="B270" s="7" t="s">
         <v>292</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" s="6">
+      <c r="E270" s="20"/>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="7">
         <v>55625</v>
       </c>
-      <c r="B271" s="6" t="s">
+      <c r="B271" s="7" t="s">
         <v>293</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272" s="6">
+      <c r="E271" s="16"/>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="7">
         <v>55501</v>
       </c>
-      <c r="B272" s="6" t="s">
+      <c r="B272" s="7" t="s">
         <v>294</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="273" spans="1:3">
-      <c r="A273" s="6">
+      <c r="E272" s="16"/>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="7">
         <v>55315</v>
       </c>
-      <c r="B273" s="6" t="s">
+      <c r="B273" s="7" t="s">
         <v>295</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="274" spans="1:3">
-      <c r="A274" s="6">
+      <c r="E273" s="26"/>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="7">
         <v>55415</v>
       </c>
-      <c r="B274" s="6" t="s">
+      <c r="B274" s="7" t="s">
         <v>296</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" s="6" t="s">
+      <c r="E274" s="16"/>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B275" s="6" t="s">
+      <c r="B275" s="7" t="s">
         <v>298</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" s="6" t="s">
+      <c r="E275" s="16"/>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="B276" s="6" t="s">
+      <c r="B276" s="7" t="s">
         <v>300</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277" s="6">
+      <c r="E276" s="16"/>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="7">
         <v>55201</v>
       </c>
-      <c r="B277" s="6" t="s">
+      <c r="B277" s="7" t="s">
         <v>301</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278" s="6">
+      <c r="E277" s="16"/>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="7">
         <v>55305</v>
       </c>
-      <c r="B278" s="6" t="s">
+      <c r="B278" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="279" spans="1:3">
-      <c r="A279" s="6">
+      <c r="E278" s="16"/>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="7">
         <v>55405</v>
       </c>
-      <c r="B279" s="6" t="s">
+      <c r="B279" s="7" t="s">
         <v>303</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="6">
+      <c r="E279" s="16"/>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="7">
         <v>55205</v>
       </c>
-      <c r="B280" s="6" t="s">
+      <c r="B280" s="7" t="s">
         <v>304</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" s="6">
+      <c r="E280" s="16"/>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="7">
         <v>55401</v>
       </c>
-      <c r="B281" s="6" t="s">
+      <c r="B281" s="7" t="s">
         <v>305</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282" s="6">
+      <c r="E281" s="16"/>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="7">
         <v>55665</v>
       </c>
-      <c r="B282" s="6" t="s">
+      <c r="B282" s="7" t="s">
         <v>306</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="283" spans="1:3">
-      <c r="A283" s="6">
+      <c r="E282" s="16"/>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="7">
         <v>55202</v>
       </c>
-      <c r="B283" s="6" t="s">
+      <c r="B283" s="7" t="s">
         <v>307</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" s="6">
+      <c r="E283" s="16"/>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="7">
         <v>55655</v>
       </c>
-      <c r="B284" s="6" t="s">
+      <c r="B284" s="7" t="s">
         <v>308</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="285" spans="1:3">
-      <c r="A285" s="6">
+      <c r="E284" s="16"/>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="7">
         <v>55115</v>
       </c>
-      <c r="B285" s="6" t="s">
+      <c r="B285" s="7" t="s">
         <v>309</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="286" spans="1:3">
-      <c r="A286" s="6">
+      <c r="E285" s="16"/>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="7">
         <v>55215</v>
       </c>
-      <c r="B286" s="6" t="s">
+      <c r="B286" s="7" t="s">
         <v>310</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="287" spans="1:3">
-      <c r="A287" s="6">
+      <c r="E286" s="16"/>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="7">
         <v>55125</v>
       </c>
-      <c r="B287" s="6" t="s">
+      <c r="B287" s="7" t="s">
         <v>311</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288" s="6">
+      <c r="E287" s="16"/>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="7">
         <v>55325</v>
       </c>
-      <c r="B288" s="6" t="s">
+      <c r="B288" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289" s="6">
+      <c r="E288" s="16"/>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="7">
         <v>54207</v>
       </c>
-      <c r="B289" s="6" t="s">
+      <c r="B289" s="7" t="s">
         <v>313</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="290" spans="1:3">
-      <c r="A290" s="6">
+      <c r="E289" s="27"/>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="7">
         <v>54111</v>
       </c>
-      <c r="B290" s="6" t="s">
+      <c r="B290" s="7" t="s">
         <v>314</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291" s="6">
+      <c r="E290" s="27"/>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="7">
         <v>55601</v>
       </c>
-      <c r="B291" s="6" t="s">
+      <c r="B291" s="7" t="s">
         <v>315</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292" s="6">
+      <c r="E291" s="16"/>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="7">
         <v>55105</v>
       </c>
-      <c r="B292" s="6" t="s">
+      <c r="B292" s="7" t="s">
         <v>316</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293" s="6">
+      <c r="E292" s="16"/>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="7">
         <v>55335</v>
       </c>
-      <c r="B293" s="6" t="s">
+      <c r="B293" s="7" t="s">
         <v>317</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294" s="6">
+      <c r="E293" s="16"/>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="7">
         <v>55302</v>
       </c>
-      <c r="B294" s="6" t="s">
+      <c r="B294" s="7" t="s">
         <v>318</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="A295" s="6">
+      <c r="E294" s="16"/>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="7">
         <v>55675</v>
       </c>
-      <c r="B295" s="6" t="s">
+      <c r="B295" s="7" t="s">
         <v>319</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="A296" s="6">
+      <c r="E295" s="16"/>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="7">
         <v>55645</v>
       </c>
-      <c r="B296" s="6" t="s">
+      <c r="B296" s="7" t="s">
         <v>320</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="297" spans="1:3">
-      <c r="A297" s="6">
+      <c r="E296" s="16"/>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="7">
         <v>55101</v>
       </c>
-      <c r="B297" s="6" t="s">
+      <c r="B297" s="7" t="s">
         <v>321</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="298" spans="1:3">
-      <c r="A298" s="6">
+      <c r="E297" s="16"/>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="7">
         <v>55605</v>
       </c>
-      <c r="B298" s="6" t="s">
+      <c r="B298" s="7" t="s">
         <v>322</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" s="6">
+      <c r="E298" s="16"/>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="7">
         <v>55602</v>
       </c>
-      <c r="B299" s="6" t="s">
+      <c r="B299" s="7" t="s">
         <v>323</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" s="6">
+      <c r="E299" s="16"/>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="7">
         <v>55615</v>
       </c>
-      <c r="B300" s="6" t="s">
+      <c r="B300" s="7" t="s">
         <v>324</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301" s="6">
+      <c r="E300" s="16"/>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="7">
         <v>55505</v>
       </c>
-      <c r="B301" s="6" t="s">
+      <c r="B301" s="7" t="s">
         <v>325</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="302" spans="1:3">
-      <c r="A302" s="6">
+      <c r="E301" s="28"/>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="7">
         <v>55301</v>
       </c>
-      <c r="B302" s="6" t="s">
+      <c r="B302" s="7" t="s">
         <v>326</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="303" spans="1:3">
-      <c r="A303" s="6">
+      <c r="E302" s="16"/>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="7">
         <v>55002</v>
       </c>
-      <c r="B303" s="6" t="s">
+      <c r="B303" s="7" t="s">
         <v>327</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="304" spans="1:3">
-      <c r="A304" s="6">
+      <c r="E303" s="26"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="7">
         <v>50001</v>
       </c>
-      <c r="B304" s="6" t="s">
+      <c r="B304" s="7" t="s">
         <v>328</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="305" spans="1:3">
-      <c r="A305" s="6">
+      <c r="E304" s="20"/>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="7">
         <v>500041</v>
       </c>
-      <c r="B305" s="6" t="s">
+      <c r="B305" s="7" t="s">
         <v>329</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="306" spans="1:3">
-      <c r="A306" s="6">
+      <c r="E305" s="16"/>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="7">
         <v>50003</v>
       </c>
-      <c r="B306" s="6" t="s">
+      <c r="B306" s="7" t="s">
         <v>330</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="307" spans="1:3">
-      <c r="A307" s="6">
+      <c r="E306" s="16"/>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="7">
         <v>54002</v>
       </c>
-      <c r="B307" s="6" t="s">
+      <c r="B307" s="7" t="s">
         <v>331</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="308" spans="1:3">
-      <c r="A308" s="6">
+      <c r="E307" s="16"/>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="7">
         <v>54106</v>
       </c>
-      <c r="B308" s="6" t="s">
+      <c r="B308" s="7" t="s">
         <v>332</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="309" spans="1:3">
-      <c r="A309" s="6">
+      <c r="E308" s="16"/>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="7">
         <v>54136</v>
       </c>
-      <c r="B309" s="6" t="s">
+      <c r="B309" s="7" t="s">
         <v>333</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="310" spans="1:3">
-      <c r="A310" s="6">
+      <c r="E309" s="29"/>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="7">
         <v>54401</v>
       </c>
-      <c r="B310" s="6" t="s">
+      <c r="B310" s="7" t="s">
         <v>334</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="311" spans="1:3">
-      <c r="A311" s="6">
+      <c r="E310" s="27"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="7">
         <v>54406</v>
       </c>
-      <c r="B311" s="6" t="s">
+      <c r="B311" s="7" t="s">
         <v>335</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="312" spans="1:3">
-      <c r="A312" s="6">
+      <c r="E311" s="27"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="7">
         <v>54206</v>
       </c>
-      <c r="B312" s="6" t="s">
+      <c r="B312" s="7" t="s">
         <v>336</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="313" spans="1:3">
-      <c r="A313" s="6">
+      <c r="E312" s="27"/>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="7">
         <v>54205</v>
       </c>
-      <c r="B313" s="6" t="s">
+      <c r="B313" s="7" t="s">
         <v>337</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="314" spans="1:3">
-      <c r="A314" s="6">
+      <c r="E313" s="27"/>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="7">
         <v>54407</v>
       </c>
-      <c r="B314" s="6" t="s">
+      <c r="B314" s="7" t="s">
         <v>338</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="315" spans="1:3">
-      <c r="A315" s="6">
+      <c r="E314" s="27"/>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="7">
         <v>54408</v>
       </c>
-      <c r="B315" s="6" t="s">
+      <c r="B315" s="7" t="s">
         <v>339</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="316" spans="1:3">
-      <c r="A316" s="6">
+      <c r="E315" s="27"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="7">
         <v>54108</v>
       </c>
-      <c r="B316" s="6" t="s">
+      <c r="B316" s="7" t="s">
         <v>340</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="317" spans="1:3">
-      <c r="A317" s="6">
+      <c r="E316" s="27"/>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="7">
         <v>54109</v>
       </c>
-      <c r="B317" s="6" t="s">
+      <c r="B317" s="7" t="s">
         <v>341</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="318" spans="1:3">
-      <c r="A318" s="6">
+      <c r="E317" s="27"/>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="7">
         <v>54201</v>
       </c>
-      <c r="B318" s="6" t="s">
+      <c r="B318" s="7" t="s">
         <v>342</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="319" spans="1:3">
-      <c r="A319" s="6">
+      <c r="E318" s="27"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="7">
         <v>54301</v>
       </c>
-      <c r="B319" s="6" t="s">
+      <c r="B319" s="7" t="s">
         <v>343</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="320" spans="1:3">
-      <c r="A320" s="6" t="s">
+      <c r="E319" s="27"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B320" s="6" t="s">
+      <c r="B320" s="7" t="s">
         <v>345</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="321" spans="1:3">
-      <c r="A321" s="6">
+      <c r="E320" s="16"/>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="7">
         <v>54110</v>
       </c>
-      <c r="B321" s="6" t="s">
+      <c r="B321" s="7" t="s">
         <v>346</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="322" spans="1:3">
-      <c r="A322" s="6">
+      <c r="E321" s="27"/>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="7">
         <v>54305</v>
       </c>
-      <c r="B322" s="6" t="s">
+      <c r="B322" s="7" t="s">
         <v>347</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="323" spans="1:3">
-      <c r="A323" s="6">
+      <c r="E322" s="27"/>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="7">
         <v>54306</v>
       </c>
-      <c r="B323" s="6" t="s">
+      <c r="B323" s="7" t="s">
         <v>348</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="324" spans="1:3">
-      <c r="A324" s="6">
+      <c r="E323" s="27"/>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="7">
         <v>54116</v>
       </c>
-      <c r="B324" s="6" t="s">
+      <c r="B324" s="7" t="s">
         <v>349</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" s="6">
+      <c r="E324" s="27"/>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="7">
         <v>54146</v>
       </c>
-      <c r="B325" s="6" t="s">
+      <c r="B325" s="7" t="s">
         <v>350</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="326" spans="1:3">
-      <c r="A326" s="6">
+      <c r="E325" s="27"/>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="7">
         <v>54126</v>
       </c>
-      <c r="B326" s="6" t="s">
+      <c r="B326" s="7" t="s">
         <v>351</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="A327" s="6">
+      <c r="E326" s="16"/>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="7">
         <v>54316</v>
       </c>
-      <c r="B327" s="6" t="s">
+      <c r="B327" s="7" t="s">
         <v>352</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="328" spans="1:3">
-      <c r="A328" s="6">
+      <c r="E327" s="16"/>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="7">
         <v>54001</v>
       </c>
-      <c r="B328" s="6" t="s">
+      <c r="B328" s="7" t="s">
         <v>353</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="329" spans="1:3">
-      <c r="A329" s="6">
+      <c r="E328" s="16"/>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="7">
         <v>500048</v>
       </c>
-      <c r="B329" s="6" t="s">
+      <c r="B329" s="7" t="s">
         <v>354</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="330" spans="1:3">
-      <c r="A330" s="6">
+      <c r="E329" s="16"/>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="7">
         <v>50002</v>
       </c>
-      <c r="B330" s="6" t="s">
+      <c r="B330" s="7" t="s">
         <v>355</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="331" spans="1:3">
-      <c r="A331" s="6">
+      <c r="E330" s="16"/>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="7">
         <v>23109</v>
       </c>
-      <c r="B331" s="6" t="s">
+      <c r="B331" s="7" t="s">
         <v>356</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="332" spans="1:3">
-      <c r="A332" s="6">
+      <c r="E331" s="16"/>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="7">
         <v>23106</v>
       </c>
-      <c r="B332" s="6" t="s">
+      <c r="B332" s="7" t="s">
         <v>357</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="333" spans="1:3">
-      <c r="A333" s="6">
+      <c r="E332" s="16"/>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="7">
         <v>23201</v>
       </c>
-      <c r="B333" s="6" t="s">
+      <c r="B333" s="7" t="s">
         <v>358</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="334" spans="1:3">
-      <c r="A334" s="6">
+      <c r="E333" s="16"/>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="7">
         <v>23202</v>
       </c>
-      <c r="B334" s="6" t="s">
+      <c r="B334" s="7" t="s">
         <v>359</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="335" spans="1:3">
-      <c r="A335" s="6">
+      <c r="E334" s="16"/>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="7">
         <v>23205</v>
       </c>
-      <c r="B335" s="6" t="s">
+      <c r="B335" s="7" t="s">
         <v>360</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="336" spans="1:3">
-      <c r="A336" s="6">
+      <c r="E335" s="16"/>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="7">
         <v>23204</v>
       </c>
-      <c r="B336" s="6" t="s">
+      <c r="B336" s="7" t="s">
         <v>361</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="337" spans="1:3">
-      <c r="A337" s="6">
+      <c r="E336" s="16"/>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="7">
         <v>23207</v>
       </c>
-      <c r="B337" s="6" t="s">
+      <c r="B337" s="7" t="s">
         <v>362</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="338" spans="1:3">
-      <c r="A338" s="6">
+      <c r="E337" s="16"/>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="7">
         <v>23208</v>
       </c>
-      <c r="B338" s="6" t="s">
+      <c r="B338" s="7" t="s">
         <v>363</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="339" spans="1:3">
-      <c r="A339" s="6">
+      <c r="E338" s="16"/>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="7">
         <v>23209</v>
       </c>
-      <c r="B339" s="6" t="s">
+      <c r="B339" s="7" t="s">
         <v>364</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="340" spans="1:3">
-      <c r="A340" s="6">
+      <c r="E339" s="16"/>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="7">
         <v>23206</v>
       </c>
-      <c r="B340" s="6" t="s">
+      <c r="B340" s="7" t="s">
         <v>365</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="341" spans="1:3">
-      <c r="A341" s="6">
+      <c r="E340" s="16"/>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="7">
         <v>23301</v>
       </c>
-      <c r="B341" s="6" t="s">
+      <c r="B341" s="7" t="s">
         <v>366</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" s="6">
+      <c r="E341" s="16"/>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="7">
         <v>23302</v>
       </c>
-      <c r="B342" s="6" t="s">
+      <c r="B342" s="7" t="s">
         <v>367</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="343" spans="1:3">
-      <c r="A343" s="6">
+      <c r="E342" s="16"/>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="7">
         <v>23305</v>
       </c>
-      <c r="B343" s="6" t="s">
+      <c r="B343" s="7" t="s">
         <v>368</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="344" spans="1:3">
-      <c r="A344" s="6">
+      <c r="E343" s="16"/>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="7">
         <v>23304</v>
       </c>
-      <c r="B344" s="6" t="s">
+      <c r="B344" s="7" t="s">
         <v>369</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="345" spans="1:3">
-      <c r="A345" s="6">
+      <c r="E344" s="16"/>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="7">
         <v>23307</v>
       </c>
-      <c r="B345" s="6" t="s">
+      <c r="B345" s="7" t="s">
         <v>370</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="346" spans="1:3">
-      <c r="A346" s="6">
+      <c r="E345" s="16"/>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="7">
         <v>23308</v>
       </c>
-      <c r="B346" s="6" t="s">
+      <c r="B346" s="7" t="s">
         <v>371</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="347" spans="1:3">
-      <c r="A347" s="6">
+      <c r="E346" s="16"/>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="7">
         <v>23306</v>
       </c>
-      <c r="B347" s="6" t="s">
+      <c r="B347" s="7" t="s">
         <v>372</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="348" spans="1:3">
-      <c r="A348" s="6">
+      <c r="E347" s="16"/>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="7">
         <v>23203</v>
       </c>
-      <c r="B348" s="6" t="s">
+      <c r="B348" s="7" t="s">
         <v>373</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="349" spans="1:3">
-      <c r="A349" s="6">
+      <c r="E348" s="16"/>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="7">
         <v>24104</v>
       </c>
-      <c r="B349" s="6" t="s">
+      <c r="B349" s="7" t="s">
         <v>374</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="350" spans="1:3">
-      <c r="A350" s="6">
+      <c r="E349" s="26"/>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="7">
         <v>24204</v>
       </c>
-      <c r="B350" s="6" t="s">
+      <c r="B350" s="7" t="s">
         <v>375</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="351" spans="1:3">
-      <c r="A351" s="6">
+      <c r="E350" s="16"/>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="7">
         <v>24205</v>
       </c>
-      <c r="B351" s="6" t="s">
+      <c r="B351" s="7" t="s">
         <v>376</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="352" spans="1:3">
-      <c r="A352" s="6">
+      <c r="E351" s="16"/>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="7">
         <v>24305</v>
       </c>
-      <c r="B352" s="6" t="s">
+      <c r="B352" s="7" t="s">
         <v>377</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353" s="6">
+      <c r="E352" s="16"/>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="7">
         <v>24304</v>
       </c>
-      <c r="B353" s="6" t="s">
+      <c r="B353" s="7" t="s">
         <v>378</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354" s="6">
+      <c r="E353" s="16"/>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="7">
         <v>24405</v>
       </c>
-      <c r="B354" s="6" t="s">
+      <c r="B354" s="7" t="s">
         <v>379</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355" s="6">
+      <c r="E354" s="16"/>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="7">
         <v>24404</v>
       </c>
-      <c r="B355" s="6" t="s">
+      <c r="B355" s="7" t="s">
         <v>380</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356" s="6">
+      <c r="E355" s="16"/>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="7">
         <v>24107</v>
       </c>
-      <c r="B356" s="6" t="s">
+      <c r="B356" s="7" t="s">
         <v>381</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="357" spans="1:3">
-      <c r="A357" s="6">
+      <c r="E356" s="16"/>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="7">
         <v>24207</v>
       </c>
-      <c r="B357" s="6" t="s">
+      <c r="B357" s="7" t="s">
         <v>382</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="358" spans="1:3">
-      <c r="A358" s="6">
+      <c r="E357" s="16"/>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="7">
         <v>24307</v>
       </c>
-      <c r="B358" s="6" t="s">
+      <c r="B358" s="7" t="s">
         <v>383</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="359" spans="1:3">
-      <c r="A359" s="6">
+      <c r="E358" s="16"/>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="7">
         <v>24407</v>
       </c>
-      <c r="B359" s="6" t="s">
+      <c r="B359" s="7" t="s">
         <v>384</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="360" spans="1:3">
-      <c r="A360" s="6">
+      <c r="E359" s="16"/>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="7">
         <v>24403</v>
       </c>
-      <c r="B360" s="6" t="s">
+      <c r="B360" s="7" t="s">
         <v>385</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="361" spans="1:3">
-      <c r="A361" s="6">
+      <c r="E360" s="16"/>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="7">
         <v>24101</v>
       </c>
-      <c r="B361" s="6" t="s">
+      <c r="B361" s="7" t="s">
         <v>386</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="362" spans="1:3">
-      <c r="A362" s="6">
+      <c r="E361" s="16"/>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="7">
         <v>24507</v>
       </c>
-      <c r="B362" s="6" t="s">
+      <c r="B362" s="7" t="s">
         <v>387</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="363" spans="1:3">
-      <c r="A363" s="6">
+      <c r="E362" s="16"/>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="7">
         <v>24508</v>
       </c>
-      <c r="B363" s="6" t="s">
+      <c r="B363" s="7" t="s">
         <v>388</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="364" spans="1:3">
-      <c r="A364" s="6">
+      <c r="E363" s="16"/>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="7">
         <v>24503</v>
       </c>
-      <c r="B364" s="6" t="s">
+      <c r="B364" s="7" t="s">
         <v>389</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="365" spans="1:3">
-      <c r="A365" s="6">
+      <c r="E364" s="16"/>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="7">
         <v>24002</v>
       </c>
-      <c r="B365" s="6" t="s">
+      <c r="B365" s="7" t="s">
         <v>390</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="366" spans="1:3">
-      <c r="A366" s="6">
+      <c r="E365" s="16"/>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="7">
         <v>24001</v>
       </c>
-      <c r="B366" s="6" t="s">
+      <c r="B366" s="7" t="s">
         <v>391</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="367" spans="1:3">
-      <c r="A367" s="6">
+      <c r="E366" s="16"/>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="7">
         <v>25001</v>
       </c>
-      <c r="B367" s="6" t="s">
+      <c r="B367" s="7" t="s">
         <v>392</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="368" spans="1:3">
-      <c r="A368" s="6">
+      <c r="E367" s="16"/>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="7">
         <v>25002</v>
       </c>
-      <c r="B368" s="6" t="s">
+      <c r="B368" s="7" t="s">
         <v>393</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="369" spans="1:3">
-      <c r="A369" s="6">
+      <c r="E368" s="16"/>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="7">
         <v>25107</v>
       </c>
-      <c r="B369" s="6" t="s">
+      <c r="B369" s="7" t="s">
         <v>394</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="370" spans="1:3">
-      <c r="A370" s="6">
+      <c r="E369" s="16"/>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="7">
         <v>25207</v>
       </c>
-      <c r="B370" s="6" t="s">
+      <c r="B370" s="7" t="s">
         <v>395</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="371" spans="1:3">
-      <c r="A371" s="6">
+      <c r="E370" s="16"/>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="7">
         <v>25108</v>
       </c>
-      <c r="B371" s="6" t="s">
+      <c r="B371" s="7" t="s">
         <v>396</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="372" spans="1:3">
-      <c r="A372" s="6">
+      <c r="E371" s="16"/>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="7">
         <v>25109</v>
       </c>
-      <c r="B372" s="6" t="s">
+      <c r="B372" s="7" t="s">
         <v>397</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="373" spans="1:3">
-      <c r="A373" s="6">
+      <c r="E372" s="16"/>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="7">
         <v>25105</v>
       </c>
-      <c r="B373" s="6" t="s">
+      <c r="B373" s="7" t="s">
         <v>398</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="374" spans="1:3">
-      <c r="A374" s="6">
+      <c r="E373" s="16"/>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="7">
         <v>25104</v>
       </c>
-      <c r="B374" s="6" t="s">
+      <c r="B374" s="7" t="s">
         <v>399</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="375" spans="1:3">
-      <c r="A375" s="6">
+      <c r="E374" s="16"/>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="7">
         <v>25201</v>
       </c>
-      <c r="B375" s="6" t="s">
+      <c r="B375" s="7" t="s">
         <v>400</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="376" spans="1:3">
-      <c r="A376" s="6">
+      <c r="E375" s="16"/>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="7">
         <v>25204</v>
       </c>
-      <c r="B376" s="6" t="s">
+      <c r="B376" s="7" t="s">
         <v>401</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="377" spans="1:3">
-      <c r="A377" s="6">
+      <c r="E376" s="16"/>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="7">
         <v>25208</v>
       </c>
-      <c r="B377" s="6" t="s">
+      <c r="B377" s="7" t="s">
         <v>402</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="378" spans="1:3">
-      <c r="A378" s="6">
+      <c r="E377" s="16"/>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="7">
         <v>25205</v>
       </c>
-      <c r="B378" s="6" t="s">
+      <c r="B378" s="7" t="s">
         <v>403</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="379" spans="1:3">
-      <c r="A379" s="6">
+      <c r="E378" s="16"/>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="7">
         <v>25304</v>
       </c>
-      <c r="B379" s="6" t="s">
+      <c r="B379" s="7" t="s">
         <v>404</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="380" spans="1:3">
-      <c r="A380" s="6">
+      <c r="E379" s="16"/>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="7">
         <v>25305</v>
       </c>
-      <c r="B380" s="6" t="s">
+      <c r="B380" s="7" t="s">
         <v>405</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="381" spans="1:3">
-      <c r="A381" s="6">
+      <c r="E380" s="16"/>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="7">
         <v>25307</v>
       </c>
-      <c r="B381" s="6" t="s">
+      <c r="B381" s="7" t="s">
         <v>406</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="382" spans="1:3">
-      <c r="A382" s="6">
+      <c r="E381" s="16"/>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="7">
         <v>25801</v>
       </c>
-      <c r="B382" s="6" t="s">
+      <c r="B382" s="7" t="s">
         <v>407</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="383" spans="1:3">
-      <c r="A383" s="6">
+      <c r="E382" s="16"/>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="7">
         <v>25501</v>
       </c>
-      <c r="B383" s="6" t="s">
+      <c r="B383" s="7" t="s">
         <v>408</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="384" spans="1:3">
-      <c r="A384" s="6">
+      <c r="E383" s="16"/>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="7">
         <v>25701</v>
       </c>
-      <c r="B384" s="6" t="s">
+      <c r="B384" s="7" t="s">
         <v>409</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="385" spans="1:3">
-      <c r="A385" s="6">
+      <c r="E384" s="16"/>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="7">
         <v>25203</v>
       </c>
-      <c r="B385" s="6" t="s">
+      <c r="B385" s="7" t="s">
         <v>410</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="386" spans="1:3">
-      <c r="A386" s="6">
+      <c r="E385" s="30"/>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="7">
         <v>25407</v>
       </c>
-      <c r="B386" s="6" t="s">
+      <c r="B386" s="7" t="s">
         <v>411</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="387" spans="1:3">
-      <c r="A387" s="6">
+      <c r="E386" s="30"/>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="7">
         <v>25806</v>
       </c>
-      <c r="B387" s="6" t="s">
+      <c r="B387" s="7" t="s">
         <v>412</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="388" spans="1:3">
-      <c r="A388" s="6">
+      <c r="E387" s="16"/>
+    </row>
+    <row r="388" ht="15.25" spans="1:5">
+      <c r="A388" s="7">
         <v>25805</v>
       </c>
-      <c r="B388" s="6" t="s">
+      <c r="B388" s="7" t="s">
         <v>413</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="389" spans="1:3">
-      <c r="A389" s="6">
+      <c r="E388" s="16"/>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="7">
         <v>25807</v>
       </c>
-      <c r="B389" s="6" t="s">
+      <c r="B389" s="7" t="s">
         <v>414</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="390" spans="1:3">
-      <c r="A390" s="6">
+      <c r="E389" s="16"/>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="7">
         <v>25507</v>
       </c>
-      <c r="B390" s="6" t="s">
+      <c r="B390" s="7" t="s">
         <v>415</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="391" spans="1:3">
-      <c r="A391" s="6">
+      <c r="E390" s="16"/>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="7">
         <v>25510</v>
       </c>
-      <c r="B391" s="6" t="s">
+      <c r="B391" s="7" t="s">
         <v>416</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="392" spans="1:3">
-      <c r="A392" s="6">
+      <c r="E391" s="16"/>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="7">
         <v>25401</v>
       </c>
-      <c r="B392" s="6" t="s">
+      <c r="B392" s="7" t="s">
         <v>417</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="393" spans="1:3">
-      <c r="A393" s="6">
+      <c r="E392" s="16"/>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="7">
         <v>24105</v>
       </c>
-      <c r="B393" s="6" t="s">
+      <c r="B393" s="7" t="s">
         <v>418</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="394" spans="1:3">
-      <c r="A394" s="6">
+      <c r="E393" s="16"/>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="7">
         <v>25402</v>
       </c>
-      <c r="B394" s="6" t="s">
+      <c r="B394" s="7" t="s">
         <v>419</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="395" spans="1:3">
-      <c r="A395" s="6">
+      <c r="E394" s="16"/>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="7">
         <v>25707</v>
       </c>
-      <c r="B395" s="6" t="s">
+      <c r="B395" s="7" t="s">
         <v>420</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="396" spans="1:3">
-      <c r="A396" s="6">
+      <c r="E395" s="16"/>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="7">
         <v>25405</v>
       </c>
-      <c r="B396" s="6" t="s">
+      <c r="B396" s="7" t="s">
         <v>421</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="397" spans="1:3">
-      <c r="A397" s="6">
+      <c r="E396" s="16"/>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="7">
         <v>25404</v>
       </c>
-      <c r="B397" s="6" t="s">
+      <c r="B397" s="7" t="s">
         <v>422</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="398" spans="1:3">
-      <c r="A398" s="6">
+      <c r="E397" s="16"/>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="7">
         <v>25601</v>
       </c>
-      <c r="B398" s="6" t="s">
+      <c r="B398" s="7" t="s">
         <v>423</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="399" spans="1:3">
-      <c r="A399" s="6">
+      <c r="E398" s="16"/>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="7">
         <v>25608</v>
       </c>
-      <c r="B399" s="6" t="s">
+      <c r="B399" s="7" t="s">
         <v>424</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="400" spans="1:3">
-      <c r="A400" s="6">
+      <c r="E399" s="16"/>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="7">
         <v>25602</v>
       </c>
-      <c r="B400" s="6" t="s">
+      <c r="B400" s="7" t="s">
         <v>425</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="401" spans="1:3">
-      <c r="A401" s="6">
+      <c r="E400" s="16"/>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="7">
         <v>25607</v>
       </c>
-      <c r="B401" s="6" t="s">
+      <c r="B401" s="7" t="s">
         <v>426</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="402" spans="1:3">
-      <c r="A402" s="6">
+      <c r="E401" s="16"/>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="7">
         <v>25702</v>
       </c>
-      <c r="B402" s="6" t="s">
+      <c r="B402" s="7" t="s">
         <v>427</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="403" spans="1:3">
-      <c r="A403" s="6">
+      <c r="E402" s="16"/>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="7">
         <v>25708</v>
       </c>
-      <c r="B403" s="6" t="s">
+      <c r="B403" s="7" t="s">
         <v>428</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="404" spans="1:3">
-      <c r="A404" s="6">
+      <c r="E403" s="16"/>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="7">
         <v>25504</v>
       </c>
-      <c r="B404" s="6" t="s">
+      <c r="B404" s="7" t="s">
         <v>429</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="405" spans="1:3">
-      <c r="A405" s="6">
+      <c r="E404" s="16"/>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="7">
         <v>25509</v>
       </c>
-      <c r="B405" s="6" t="s">
+      <c r="B405" s="7" t="s">
         <v>430</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="406" spans="1:3">
-      <c r="A406" s="6">
+      <c r="E405" s="16"/>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="7">
         <v>14001</v>
       </c>
-      <c r="B406" s="6" t="s">
+      <c r="B406" s="7" t="s">
         <v>431</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="407" spans="1:3">
-      <c r="A407" s="6">
+      <c r="E406" s="31"/>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="7">
         <v>14103</v>
       </c>
-      <c r="B407" s="6" t="s">
+      <c r="B407" s="7" t="s">
         <v>432</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="408" spans="1:3">
-      <c r="A408" s="6">
+      <c r="E407" s="31"/>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="7">
         <v>14105</v>
       </c>
-      <c r="B408" s="6" t="s">
+      <c r="B408" s="7" t="s">
         <v>433</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="409" spans="1:3">
-      <c r="A409" s="6">
+      <c r="E408" s="8"/>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="7">
         <v>14106</v>
       </c>
-      <c r="B409" s="6" t="s">
+      <c r="B409" s="7" t="s">
         <v>434</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="410" spans="1:3">
-      <c r="A410" s="6">
+      <c r="E409" s="31"/>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="7">
         <v>14107</v>
       </c>
-      <c r="B410" s="6" t="s">
+      <c r="B410" s="7" t="s">
         <v>435</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="411" spans="1:3">
-      <c r="A411" s="6">
+      <c r="E410" s="31"/>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="7">
         <v>14204</v>
       </c>
-      <c r="B411" s="6" t="s">
+      <c r="B411" s="7" t="s">
         <v>436</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="412" spans="1:3">
-      <c r="A412" s="6">
+      <c r="E411" s="31"/>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="7">
         <v>14206</v>
       </c>
-      <c r="B412" s="6" t="s">
+      <c r="B412" s="7" t="s">
         <v>437</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="413" spans="1:3">
-      <c r="A413" s="6">
+      <c r="E412" s="31"/>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="7">
         <v>14207</v>
       </c>
-      <c r="B413" s="6" t="s">
+      <c r="B413" s="7" t="s">
         <v>438</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="414" spans="1:3">
-      <c r="A414" s="6">
+      <c r="E413" s="31"/>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="7">
         <v>14208</v>
       </c>
-      <c r="B414" s="6" t="s">
+      <c r="B414" s="7" t="s">
         <v>439</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="415" spans="1:3">
-      <c r="A415" s="6">
+      <c r="E414" s="31"/>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="7">
         <v>14209</v>
       </c>
-      <c r="B415" s="6" t="s">
+      <c r="B415" s="7" t="s">
         <v>440</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="416" spans="1:3">
-      <c r="A416" s="6">
+      <c r="E415" s="32"/>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="7">
         <v>14210</v>
       </c>
-      <c r="B416" s="6" t="s">
+      <c r="B416" s="7" t="s">
         <v>441</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="417" spans="1:3">
-      <c r="A417" s="6">
+      <c r="E416" s="31"/>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="7">
         <v>14304</v>
       </c>
-      <c r="B417" s="6" t="s">
+      <c r="B417" s="7" t="s">
         <v>442</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="418" spans="1:3">
-      <c r="A418" s="6">
+      <c r="E417" s="31"/>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="7">
         <v>14308</v>
       </c>
-      <c r="B418" s="6" t="s">
+      <c r="B418" s="7" t="s">
         <v>443</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="419" spans="1:3">
-      <c r="A419" s="6">
+      <c r="E418" s="31"/>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="7">
         <v>14605</v>
       </c>
-      <c r="B419" s="6" t="s">
+      <c r="B419" s="7" t="s">
         <v>444</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="420" spans="1:3">
-      <c r="A420" s="6">
+      <c r="E419" s="8"/>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="7">
         <v>14307</v>
       </c>
-      <c r="B420" s="6" t="s">
+      <c r="B420" s="7" t="s">
         <v>445</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="421" spans="1:3">
-      <c r="A421" s="6">
+      <c r="E420" s="8"/>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="7">
         <v>14501</v>
       </c>
-      <c r="B421" s="6" t="s">
+      <c r="B421" s="7" t="s">
         <v>446</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="422" spans="1:3">
-      <c r="A422" s="6">
+      <c r="E421" s="8"/>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="7">
         <v>14507</v>
       </c>
-      <c r="B422" s="6" t="s">
+      <c r="B422" s="7" t="s">
         <v>447</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="423" spans="1:3">
-      <c r="A423" s="6">
+      <c r="E422" s="8"/>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="7">
         <v>14503</v>
       </c>
-      <c r="B423" s="6" t="s">
+      <c r="B423" s="7" t="s">
         <v>448</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="424" spans="1:3">
-      <c r="A424" s="6">
+      <c r="E423" s="8"/>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="7">
         <v>14505</v>
       </c>
-      <c r="B424" s="6" t="s">
+      <c r="B424" s="7" t="s">
         <v>449</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="425" spans="1:3">
-      <c r="A425" s="6">
+      <c r="E424" s="8"/>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="7">
         <v>14707</v>
       </c>
-      <c r="B425" s="6" t="s">
+      <c r="B425" s="7" t="s">
         <v>450</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="426" spans="1:3">
-      <c r="A426" s="6">
+      <c r="E425" s="8"/>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="7">
         <v>14504</v>
       </c>
-      <c r="B426" s="6" t="s">
+      <c r="B426" s="7" t="s">
         <v>451</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="427" spans="1:3">
-      <c r="A427" s="6">
+      <c r="E426" s="8"/>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="7">
         <v>14508</v>
       </c>
-      <c r="B427" s="6" t="s">
+      <c r="B427" s="7" t="s">
         <v>452</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="428" spans="1:3">
-      <c r="A428" s="6">
+      <c r="E427" s="8"/>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="7">
         <v>14705</v>
       </c>
-      <c r="B428" s="6" t="s">
+      <c r="B428" s="7" t="s">
         <v>453</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="429" spans="1:3">
-      <c r="A429" s="6">
+      <c r="E428" s="8"/>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="7">
         <v>14706</v>
       </c>
-      <c r="B429" s="6" t="s">
+      <c r="B429" s="7" t="s">
         <v>454</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="430" spans="1:3">
-      <c r="A430" s="6">
+      <c r="E429" s="8"/>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="7">
         <v>14601</v>
       </c>
-      <c r="B430" s="6" t="s">
+      <c r="B430" s="7" t="s">
         <v>455</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="431" spans="1:3">
-      <c r="A431" s="6">
+      <c r="E430" s="8"/>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="7">
         <v>14602</v>
       </c>
-      <c r="B431" s="6" t="s">
+      <c r="B431" s="7" t="s">
         <v>456</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="432" spans="1:3">
-      <c r="A432" s="6">
+      <c r="E431" s="8"/>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="7">
         <v>14301</v>
       </c>
-      <c r="B432" s="6" t="s">
+      <c r="B432" s="7" t="s">
         <v>457</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="433" spans="1:3">
-      <c r="A433" s="6">
+      <c r="E432" s="8"/>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="7">
         <v>14305</v>
       </c>
-      <c r="B433" s="6" t="s">
+      <c r="B433" s="7" t="s">
         <v>458</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="434" spans="1:3">
-      <c r="A434" s="6">
+      <c r="E433" s="8"/>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="7">
         <v>14203</v>
       </c>
-      <c r="B434" s="6" t="s">
+      <c r="B434" s="7" t="s">
         <v>459</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="435" spans="1:3">
-      <c r="A435" s="6">
+      <c r="E434" s="31"/>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="7">
         <v>14615</v>
       </c>
-      <c r="B435" s="6" t="s">
+      <c r="B435" s="7" t="s">
         <v>460</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="436" spans="1:3">
-      <c r="A436" s="6">
+      <c r="E435" s="31"/>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="7">
         <v>14108</v>
       </c>
-      <c r="B436" s="6" t="s">
+      <c r="B436" s="7" t="s">
         <v>461</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="437" spans="1:3">
-      <c r="A437" s="6">
+      <c r="E436" s="31"/>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="7">
         <v>14104</v>
       </c>
-      <c r="B437" s="6" t="s">
+      <c r="B437" s="7" t="s">
         <v>462</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="438" spans="1:3">
-      <c r="A438" s="6">
+      <c r="E437" s="31"/>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="7">
         <v>14109</v>
       </c>
-      <c r="B438" s="6" t="s">
+      <c r="B438" s="7" t="s">
         <v>463</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="439" spans="1:3">
-      <c r="A439" s="6">
+      <c r="E438" s="31"/>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="7">
         <v>14111</v>
       </c>
-      <c r="B439" s="6" t="s">
+      <c r="B439" s="7" t="s">
         <v>464</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="440" spans="1:3">
-      <c r="A440" s="6">
+      <c r="E439" s="31"/>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="7">
         <v>14002</v>
       </c>
-      <c r="B440" s="6" t="s">
+      <c r="B440" s="7" t="s">
         <v>465</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="441" spans="1:3">
-      <c r="A441" s="6">
+      <c r="E440" s="8"/>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="7">
         <v>14205</v>
       </c>
-      <c r="B441" s="6" t="s">
+      <c r="B441" s="7" t="s">
         <v>466</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="442" spans="1:3">
-      <c r="A442" s="6">
+      <c r="E441" s="31"/>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="7">
         <v>14401</v>
       </c>
-      <c r="B442" s="6" t="s">
+      <c r="B442" s="7" t="s">
         <v>467</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="443" spans="1:3">
-      <c r="A443" s="6">
+      <c r="E442" s="8"/>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="7">
         <v>14402</v>
       </c>
-      <c r="B443" s="6" t="s">
+      <c r="B443" s="7" t="s">
         <v>468</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="444" spans="1:3">
-      <c r="A444" s="6">
+      <c r="E443" s="8"/>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="7">
         <v>11001</v>
       </c>
-      <c r="B444" s="6" t="s">
+      <c r="B444" s="7" t="s">
         <v>469</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="445" spans="1:3">
-      <c r="A445" s="6">
+      <c r="E444" s="33"/>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="7">
         <v>11110</v>
       </c>
-      <c r="B445" s="6" t="s">
+      <c r="B445" s="7" t="s">
         <v>470</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="446" spans="1:3">
-      <c r="A446" s="6">
+      <c r="E445" s="11"/>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="7">
         <v>11106</v>
       </c>
-      <c r="B446" s="6" t="s">
+      <c r="B446" s="7" t="s">
         <v>471</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="447" spans="1:3">
-      <c r="A447" s="6">
+      <c r="E446" s="11"/>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="7">
         <v>11103</v>
       </c>
-      <c r="B447" s="6" t="s">
+      <c r="B447" s="7" t="s">
         <v>472</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="448" spans="1:3">
-      <c r="A448" s="6">
+      <c r="E447" s="11"/>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="7">
         <v>11108</v>
       </c>
-      <c r="B448" s="6" t="s">
+      <c r="B448" s="7" t="s">
         <v>473</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="449" spans="1:3">
-      <c r="A449" s="6">
+      <c r="E448" s="11"/>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="7">
         <v>11109</v>
       </c>
-      <c r="B449" s="6" t="s">
+      <c r="B449" s="7" t="s">
         <v>474</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="450" spans="1:3">
-      <c r="A450" s="6">
+      <c r="E449" s="9"/>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="7">
         <v>11201</v>
       </c>
-      <c r="B450" s="6" t="s">
+      <c r="B450" s="7" t="s">
         <v>475</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="451" spans="1:3">
-      <c r="A451" s="6">
+      <c r="E450" s="11"/>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="7">
         <v>11202</v>
       </c>
-      <c r="B451" s="6" t="s">
+      <c r="B451" s="7" t="s">
         <v>476</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="452" spans="1:3">
-      <c r="A452" s="6">
+      <c r="E451" s="11"/>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="7">
         <v>11204</v>
       </c>
-      <c r="B452" s="6" t="s">
+      <c r="B452" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="C452" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3">
-      <c r="A453" s="6">
+      <c r="C452" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E452" s="11"/>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="7">
         <v>11205</v>
       </c>
-      <c r="B453" s="6" t="s">
+      <c r="B453" s="7" t="s">
         <v>478</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="454" spans="1:3">
-      <c r="A454" s="6">
+      <c r="E453" s="11"/>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="7">
         <v>11208</v>
       </c>
-      <c r="B454" s="6" t="s">
+      <c r="B454" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="C454" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3">
-      <c r="A455" s="6">
+      <c r="C454" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E454" s="11"/>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="7">
         <v>11207</v>
       </c>
-      <c r="B455" s="6" t="s">
+      <c r="B455" s="7" t="s">
         <v>480</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="456" spans="1:3">
-      <c r="A456" s="6">
+      <c r="E455" s="12"/>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="7">
         <v>11209</v>
       </c>
-      <c r="B456" s="6" t="s">
+      <c r="B456" s="7" t="s">
         <v>481</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="457" spans="1:3">
-      <c r="A457" s="6">
+      <c r="E456" s="34"/>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="7">
         <v>11206</v>
       </c>
-      <c r="B457" s="6" t="s">
+      <c r="B457" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="458" spans="1:3">
-      <c r="A458" s="6">
+      <c r="E457" s="11"/>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="7">
         <v>11301</v>
       </c>
-      <c r="B458" s="6" t="s">
+      <c r="B458" s="7" t="s">
         <v>483</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="459" spans="1:3">
-      <c r="A459" s="6">
+      <c r="E458" s="11"/>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="7">
         <v>11302</v>
       </c>
-      <c r="B459" s="6" t="s">
+      <c r="B459" s="7" t="s">
         <v>484</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="460" spans="1:3">
-      <c r="A460" s="6">
+      <c r="E459" s="11"/>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="7">
         <v>11308</v>
       </c>
-      <c r="B460" s="6" t="s">
+      <c r="B460" s="7" t="s">
         <v>485</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="461" spans="1:3">
-      <c r="A461" s="6">
+      <c r="E460" s="11"/>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="7">
         <v>11307</v>
       </c>
-      <c r="B461" s="6" t="s">
+      <c r="B461" s="7" t="s">
         <v>486</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="462" spans="1:3">
-      <c r="A462" s="6">
+      <c r="E461" s="10"/>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="7">
         <v>11002</v>
       </c>
-      <c r="B462" s="6" t="s">
+      <c r="B462" s="7" t="s">
         <v>487</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="463" spans="1:3">
-      <c r="A463" s="6">
+      <c r="E462" s="11"/>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="7">
         <v>14407</v>
       </c>
-      <c r="B463" s="6" t="s">
+      <c r="B463" s="7" t="s">
         <v>488</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="464" spans="1:3">
-      <c r="A464" s="6">
+      <c r="E463" s="8"/>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="7">
         <v>14405</v>
       </c>
-      <c r="B464" s="6" t="s">
+      <c r="B464" s="7" t="s">
         <v>489</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="465" spans="1:3">
-      <c r="A465" s="6">
+      <c r="E464" s="31"/>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="7">
         <v>11303</v>
       </c>
-      <c r="B465" s="6" t="s">
+      <c r="B465" s="7" t="s">
         <v>490</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="466" spans="1:3">
-      <c r="A466" s="6">
+      <c r="E465" s="11"/>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="7">
         <v>11309</v>
       </c>
-      <c r="B466" s="6" t="s">
+      <c r="B466" s="7" t="s">
         <v>491</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="467" spans="1:3">
-      <c r="A467" s="6">
+      <c r="E466" s="11"/>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="7">
         <v>11304</v>
       </c>
-      <c r="B467" s="6" t="s">
+      <c r="B467" s="7" t="s">
         <v>492</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="468" spans="1:3">
-      <c r="A468" s="6">
+      <c r="E467" s="9"/>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="7">
         <v>11305</v>
       </c>
-      <c r="B468" s="6" t="s">
+      <c r="B468" s="7" t="s">
         <v>493</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="469" spans="1:3">
-      <c r="A469" s="6">
+      <c r="E468" s="11"/>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="7">
         <v>11310</v>
       </c>
-      <c r="B469" s="6" t="s">
+      <c r="B469" s="7" t="s">
         <v>494</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="470" spans="1:3">
-      <c r="A470" s="6">
+      <c r="E469" s="11"/>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="7">
         <v>11306</v>
       </c>
-      <c r="B470" s="6" t="s">
+      <c r="B470" s="7" t="s">
         <v>495</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="471" spans="1:3">
-      <c r="A471" s="6">
+      <c r="E470" s="11"/>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="7">
         <v>11203</v>
       </c>
-      <c r="B471" s="6" t="s">
+      <c r="B471" s="7" t="s">
         <v>496</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="472" spans="1:3">
-      <c r="A472" s="6">
+      <c r="E471" s="9"/>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="7">
         <v>11210</v>
       </c>
-      <c r="B472" s="6" t="s">
+      <c r="B472" s="7" t="s">
         <v>497</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="473" spans="1:3">
-      <c r="A473" s="6">
+      <c r="E472" s="9"/>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="7">
         <v>11104</v>
       </c>
-      <c r="B473" s="6" t="s">
+      <c r="B473" s="7" t="s">
         <v>498</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="474" spans="1:3">
-      <c r="A474" s="6">
+      <c r="E473" s="11"/>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="7">
         <v>11105</v>
       </c>
-      <c r="B474" s="6" t="s">
+      <c r="B474" s="7" t="s">
         <v>499</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="475" spans="1:3">
-      <c r="A475" s="6">
+      <c r="E474" s="11"/>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="7">
         <v>11111</v>
       </c>
-      <c r="B475" s="6" t="s">
+      <c r="B475" s="7" t="s">
         <v>500</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="476" spans="1:3">
-      <c r="A476" s="6">
+      <c r="E475" s="11"/>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="7">
         <v>11107</v>
       </c>
-      <c r="B476" s="6" t="s">
+      <c r="B476" s="7" t="s">
         <v>501</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="477" spans="1:3">
-      <c r="A477" s="6">
+      <c r="E476" s="11"/>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="7">
         <v>11101</v>
       </c>
-      <c r="B477" s="6" t="s">
+      <c r="B477" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="C477" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3">
-      <c r="A478" s="6">
+      <c r="C477" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E477" s="11"/>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="7">
         <v>11102</v>
       </c>
-      <c r="B478" s="6" t="s">
+      <c r="B478" s="7" t="s">
         <v>503</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="479" spans="1:3">
-      <c r="A479" s="6">
+      <c r="E478" s="11"/>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="7">
         <v>10001</v>
       </c>
-      <c r="B479" s="6" t="s">
+      <c r="B479" s="7" t="s">
         <v>504</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="480" spans="1:3">
-      <c r="A480" s="6">
+      <c r="E479" s="16"/>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="7">
         <v>71001</v>
       </c>
-      <c r="B480" s="6" t="s">
+      <c r="B480" s="7" t="s">
         <v>505</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="481" spans="1:3">
-      <c r="A481" s="6">
+      <c r="E480" s="15"/>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="7">
         <v>71003</v>
       </c>
-      <c r="B481" s="6" t="s">
+      <c r="B481" s="7" t="s">
         <v>506</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="482" spans="1:3">
-      <c r="A482" s="6">
+      <c r="E481" s="15"/>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" s="7">
         <v>71004</v>
       </c>
-      <c r="B482" s="6" t="s">
+      <c r="B482" s="7" t="s">
         <v>507</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="483" spans="1:3">
-      <c r="A483" s="6">
+      <c r="E482" s="15"/>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" s="7">
         <v>71036</v>
       </c>
-      <c r="B483" s="6" t="s">
+      <c r="B483" s="7" t="s">
         <v>508</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="484" spans="1:3">
-      <c r="A484" s="6">
+      <c r="E483" s="15"/>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" s="7">
         <v>71037</v>
       </c>
-      <c r="B484" s="6" t="s">
+      <c r="B484" s="7" t="s">
         <v>509</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="485" spans="1:3">
-      <c r="A485" s="6">
+      <c r="E484" s="35"/>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485" s="7">
         <v>71038</v>
       </c>
-      <c r="B485" s="6" t="s">
+      <c r="B485" s="7" t="s">
         <v>510</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="486" spans="1:3">
-      <c r="A486" s="6">
+      <c r="E485" s="35"/>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486" s="7">
         <v>71043</v>
       </c>
-      <c r="B486" s="6" t="s">
+      <c r="B486" s="7" t="s">
         <v>511</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="487" spans="1:3">
-      <c r="A487" s="6">
+      <c r="E486" s="15"/>
+    </row>
+    <row r="487" spans="1:5">
+      <c r="A487" s="7">
         <v>71041</v>
       </c>
-      <c r="B487" s="6" t="s">
+      <c r="B487" s="7" t="s">
         <v>512</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="488" spans="1:3">
-      <c r="A488" s="6">
+      <c r="E487" s="36"/>
+    </row>
+    <row r="488" spans="1:5">
+      <c r="A488" s="7">
         <v>71042</v>
       </c>
-      <c r="B488" s="6" t="s">
+      <c r="B488" s="7" t="s">
         <v>513</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="489" spans="1:3">
-      <c r="A489" s="6">
+      <c r="E488" s="36"/>
+    </row>
+    <row r="489" spans="1:5">
+      <c r="A489" s="7">
         <v>71046</v>
       </c>
-      <c r="B489" s="6" t="s">
+      <c r="B489" s="7" t="s">
         <v>514</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="490" spans="1:3">
-      <c r="A490" s="6">
+      <c r="E489" s="15"/>
+    </row>
+    <row r="490" spans="1:5">
+      <c r="A490" s="7">
         <v>71048</v>
       </c>
-      <c r="B490" s="6" t="s">
+      <c r="B490" s="7" t="s">
         <v>515</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="491" spans="1:3">
-      <c r="A491" s="6">
+      <c r="E490" s="15"/>
+    </row>
+    <row r="491" spans="1:5">
+      <c r="A491" s="7">
         <v>71026</v>
       </c>
-      <c r="B491" s="6" t="s">
+      <c r="B491" s="7" t="s">
         <v>516</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="492" spans="1:3">
-      <c r="A492" s="6">
+      <c r="E491" s="37"/>
+    </row>
+    <row r="492" spans="1:5">
+      <c r="A492" s="7">
         <v>71061</v>
       </c>
-      <c r="B492" s="6" t="s">
+      <c r="B492" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="493" spans="1:3">
-      <c r="A493" s="6">
+      <c r="E492" s="38"/>
+    </row>
+    <row r="493" spans="1:5">
+      <c r="A493" s="7">
         <v>71062</v>
       </c>
-      <c r="B493" s="6" t="s">
+      <c r="B493" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="C493" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3">
-      <c r="A494" s="6">
+      <c r="C493" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E493" s="38"/>
+    </row>
+    <row r="494" spans="1:5">
+      <c r="A494" s="7">
         <v>71063</v>
       </c>
-      <c r="B494" s="6" t="s">
+      <c r="B494" s="7" t="s">
         <v>519</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="495" spans="1:3">
-      <c r="A495" s="6">
+      <c r="E494" s="39"/>
+    </row>
+    <row r="495" spans="1:5">
+      <c r="A495" s="7">
         <v>80001</v>
       </c>
-      <c r="B495" s="6" t="s">
+      <c r="B495" s="7" t="s">
         <v>520</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="496" spans="1:3">
-      <c r="A496" s="6">
+      <c r="E495" s="40"/>
+    </row>
+    <row r="496" spans="1:5">
+      <c r="A496" s="7">
         <v>71072</v>
       </c>
-      <c r="B496" s="6" t="s">
+      <c r="B496" s="7" t="s">
         <v>521</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="497" spans="1:3">
-      <c r="A497" s="6">
+      <c r="E496" s="39"/>
+    </row>
+    <row r="497" spans="1:5">
+      <c r="A497" s="7">
         <v>71076</v>
       </c>
-      <c r="B497" s="6" t="s">
+      <c r="B497" s="7" t="s">
         <v>522</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="498" spans="1:3">
-      <c r="A498" s="6">
+      <c r="E497" s="39"/>
+    </row>
+    <row r="498" spans="1:5">
+      <c r="A498" s="7">
         <v>71013</v>
       </c>
-      <c r="B498" s="6" t="s">
+      <c r="B498" s="7" t="s">
         <v>523</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="499" spans="1:3">
-      <c r="A499" s="6">
+      <c r="E498" s="39"/>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499" s="7">
         <v>710012</v>
       </c>
-      <c r="B499" s="6" t="s">
+      <c r="B499" s="7" t="s">
         <v>524</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="500" spans="1:3">
-      <c r="A500" s="6">
+      <c r="E499" s="39"/>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500" s="7">
         <v>71011</v>
       </c>
-      <c r="B500" s="6" t="s">
+      <c r="B500" s="7" t="s">
         <v>525</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="501" spans="1:3">
-      <c r="A501" s="6">
+      <c r="E500" s="39"/>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501" s="7">
         <v>71022</v>
       </c>
-      <c r="B501" s="6" t="s">
+      <c r="B501" s="7" t="s">
         <v>526</v>
       </c>
       <c r="C501" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="502" spans="1:3">
-      <c r="A502" s="6">
+      <c r="E501" s="36"/>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502" s="7">
         <v>71023</v>
       </c>
-      <c r="B502" s="6" t="s">
+      <c r="B502" s="7" t="s">
         <v>527</v>
       </c>
       <c r="C502" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="503" spans="1:3">
-      <c r="A503" s="6">
+      <c r="E502" s="35"/>
+    </row>
+    <row r="503" spans="1:5">
+      <c r="A503" s="7">
         <v>71021</v>
       </c>
-      <c r="B503" s="6" t="s">
+      <c r="B503" s="7" t="s">
         <v>528</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="504" spans="1:3">
-      <c r="A504" s="6">
+      <c r="E503" s="36"/>
+    </row>
+    <row r="504" spans="1:5">
+      <c r="A504" s="7">
         <v>71034</v>
       </c>
-      <c r="B504" s="6" t="s">
+      <c r="B504" s="7" t="s">
         <v>529</v>
       </c>
       <c r="C504" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="505" spans="1:3">
-      <c r="A505" s="6">
+      <c r="E504" s="15"/>
+    </row>
+    <row r="505" spans="1:5">
+      <c r="A505" s="7">
         <v>71033</v>
       </c>
-      <c r="B505" s="6" t="s">
+      <c r="B505" s="7" t="s">
         <v>530</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="506" spans="1:3">
-      <c r="A506" s="6">
+      <c r="E505" s="38"/>
+    </row>
+    <row r="506" spans="1:5">
+      <c r="A506" s="7">
         <v>71032</v>
       </c>
-      <c r="B506" s="6" t="s">
+      <c r="B506" s="7" t="s">
         <v>531</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="507" spans="1:3">
-      <c r="A507" s="6">
+      <c r="E506" s="15"/>
+    </row>
+    <row r="507" spans="1:5">
+      <c r="A507" s="7">
         <v>71031</v>
       </c>
-      <c r="B507" s="6" t="s">
+      <c r="B507" s="7" t="s">
         <v>532</v>
       </c>
       <c r="C507" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="508" spans="1:3">
-      <c r="A508" s="6">
+      <c r="E507" s="15"/>
+    </row>
+    <row r="508" spans="1:5">
+      <c r="A508" s="7">
         <v>71002</v>
       </c>
-      <c r="B508" s="6" t="s">
+      <c r="B508" s="7" t="s">
         <v>533</v>
       </c>
       <c r="C508" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="509" spans="1:3">
-      <c r="A509" s="6">
+      <c r="E508" s="15"/>
+    </row>
+    <row r="509" spans="1:5">
+      <c r="A509" s="7">
         <v>99940</v>
       </c>
-      <c r="B509" s="6" t="s">
+      <c r="B509" s="7" t="s">
         <v>534</v>
       </c>
       <c r="C509" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="510" spans="1:3">
-      <c r="A510" s="6">
+      <c r="E509" s="41"/>
+    </row>
+    <row r="510" spans="1:5">
+      <c r="A510" s="7">
         <v>12310</v>
       </c>
-      <c r="B510" s="6" t="s">
+      <c r="B510" s="7" t="s">
         <v>535</v>
       </c>
       <c r="C510" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="511" spans="1:3">
-      <c r="A511" s="6">
-        <v>14701</v>
-      </c>
-      <c r="B511" s="6" t="s">
+      <c r="E510" s="42"/>
+    </row>
+    <row r="511" spans="1:5">
+      <c r="A511" s="7">
+        <v>99941</v>
+      </c>
+      <c r="B511" s="7" t="s">
         <v>536</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="512" spans="1:3">
-      <c r="A512" s="6">
-        <v>99941</v>
-      </c>
-      <c r="B512" s="6" t="s">
+      <c r="E511" s="41"/>
+    </row>
+    <row r="512" spans="1:5">
+      <c r="A512" s="7">
+        <v>99948</v>
+      </c>
+      <c r="B512" s="7" t="s">
         <v>537</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="513" spans="1:3">
-      <c r="A513" s="6">
-        <v>99948</v>
-      </c>
-      <c r="B513" s="6" t="s">
+      <c r="E512" s="25"/>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513" s="7">
+        <v>99949</v>
+      </c>
+      <c r="B513" s="7" t="s">
         <v>538</v>
       </c>
       <c r="C513" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="514" spans="1:3">
-      <c r="A514" s="6">
-        <v>99949</v>
-      </c>
-      <c r="B514" s="6" t="s">
+      <c r="E513" s="25"/>
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514" s="7">
+        <v>99950</v>
+      </c>
+      <c r="B514" s="7" t="s">
         <v>539</v>
       </c>
       <c r="C514" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="515" spans="1:3">
-      <c r="A515" s="6">
-        <v>99950</v>
-      </c>
-      <c r="B515" s="6" t="s">
+      <c r="E514" s="25"/>
+    </row>
+    <row r="515" spans="1:5">
+      <c r="A515" s="7">
+        <v>99951</v>
+      </c>
+      <c r="B515" s="7" t="s">
         <v>540</v>
       </c>
       <c r="C515" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="516" spans="1:3">
-      <c r="A516" s="6">
-        <v>99951</v>
-      </c>
-      <c r="B516" s="6" t="s">
+      <c r="E515" s="25"/>
+    </row>
+    <row r="516" spans="1:5">
+      <c r="A516" s="7">
+        <v>99952</v>
+      </c>
+      <c r="B516" s="7" t="s">
         <v>541</v>
       </c>
       <c r="C516" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="517" spans="1:3">
-      <c r="A517" s="6">
-        <v>99952</v>
-      </c>
-      <c r="B517" s="6" t="s">
+      <c r="E516" s="25"/>
+    </row>
+    <row r="517" spans="1:5">
+      <c r="A517" s="7">
+        <v>99953</v>
+      </c>
+      <c r="B517" s="7" t="s">
         <v>542</v>
       </c>
       <c r="C517" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="518" spans="1:3">
-      <c r="A518" s="6">
-        <v>99953</v>
-      </c>
-      <c r="B518" s="6" t="s">
+      <c r="E517" s="25"/>
+    </row>
+    <row r="518" spans="1:5">
+      <c r="A518" s="7">
+        <v>99954</v>
+      </c>
+      <c r="B518" s="7" t="s">
         <v>543</v>
       </c>
       <c r="C518" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="519" spans="1:3">
-      <c r="A519" s="6">
-        <v>99954</v>
-      </c>
-      <c r="B519" s="6" t="s">
+      <c r="E518" s="25"/>
+    </row>
+    <row r="519" spans="1:5">
+      <c r="A519" s="7">
+        <v>99955</v>
+      </c>
+      <c r="B519" s="7" t="s">
         <v>544</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="520" spans="1:3">
-      <c r="A520" s="6">
-        <v>99955</v>
-      </c>
-      <c r="B520" s="6" t="s">
+      <c r="E519" s="25"/>
+    </row>
+    <row r="520" spans="1:5">
+      <c r="A520" s="7">
+        <v>99956</v>
+      </c>
+      <c r="B520" s="7" t="s">
         <v>545</v>
       </c>
       <c r="C520" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="521" spans="1:3">
-      <c r="A521" s="6">
-        <v>99956</v>
-      </c>
-      <c r="B521" s="6" t="s">
+      <c r="E520" s="25"/>
+    </row>
+    <row r="521" spans="1:5">
+      <c r="A521" s="7">
+        <v>99957</v>
+      </c>
+      <c r="B521" s="7" t="s">
         <v>546</v>
       </c>
       <c r="C521" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="522" spans="1:3">
-      <c r="A522" s="6">
-        <v>99957</v>
-      </c>
-      <c r="B522" s="6" t="s">
+      <c r="E521" s="25"/>
+    </row>
+    <row r="522" spans="1:5">
+      <c r="A522" s="7">
+        <v>99958</v>
+      </c>
+      <c r="B522" s="7" t="s">
         <v>547</v>
       </c>
       <c r="C522" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="523" spans="1:3">
-      <c r="A523" s="6">
-        <v>99958</v>
-      </c>
-      <c r="B523" s="6" t="s">
+      <c r="E522" s="25"/>
+    </row>
+    <row r="523" spans="1:5">
+      <c r="A523" s="7">
+        <v>99946</v>
+      </c>
+      <c r="B523" s="7" t="s">
         <v>548</v>
       </c>
       <c r="C523" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="524" spans="1:3">
-      <c r="A524" s="6">
-        <v>99946</v>
-      </c>
-      <c r="B524" s="6" t="s">
+      <c r="E523" s="25"/>
+    </row>
+    <row r="524" spans="1:5">
+      <c r="A524" s="7">
+        <v>99947</v>
+      </c>
+      <c r="B524" s="7" t="s">
         <v>549</v>
       </c>
       <c r="C524" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="525" spans="1:3">
-      <c r="A525" s="6">
-        <v>99947</v>
-      </c>
-      <c r="B525" s="6" t="s">
+      <c r="E524" s="25"/>
+    </row>
+    <row r="525" spans="1:5">
+      <c r="A525" s="7">
+        <v>99944</v>
+      </c>
+      <c r="B525" s="7" t="s">
         <v>550</v>
       </c>
       <c r="C525" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="526" spans="1:3">
-      <c r="A526" s="6">
-        <v>99944</v>
-      </c>
-      <c r="B526" s="6" t="s">
+      <c r="E525" s="25"/>
+    </row>
+    <row r="526" spans="1:5">
+      <c r="A526" s="7">
+        <v>99945</v>
+      </c>
+      <c r="B526" s="7" t="s">
         <v>551</v>
       </c>
       <c r="C526" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="527" spans="1:3">
-      <c r="A527" s="6">
-        <v>99945</v>
-      </c>
-      <c r="B527" s="6" t="s">
+      <c r="E526" s="25"/>
+    </row>
+    <row r="527" spans="1:5">
+      <c r="A527" s="7">
+        <v>99942</v>
+      </c>
+      <c r="B527" s="7" t="s">
         <v>552</v>
       </c>
       <c r="C527" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="528" spans="1:3">
-      <c r="A528" s="6">
-        <v>99942</v>
-      </c>
-      <c r="B528" s="6" t="s">
+      <c r="E527" s="25"/>
+    </row>
+    <row r="528" spans="1:5">
+      <c r="A528" s="7">
+        <v>99943</v>
+      </c>
+      <c r="B528" s="7" t="s">
         <v>553</v>
       </c>
       <c r="C528" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E528" s="43"/>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="6">
-        <v>99943</v>
-      </c>
-      <c r="B529" s="6" t="s">
+      <c r="A529" s="7">
+        <v>167039</v>
+      </c>
+      <c r="B529" s="7" t="s">
         <v>554</v>
       </c>
       <c r="C529" s="1" t="s">
@@ -8649,10 +9315,10 @@
       </c>
     </row>
     <row r="530" spans="1:3">
-      <c r="A530" s="6">
-        <v>167039</v>
-      </c>
-      <c r="B530" s="6" t="s">
+      <c r="A530" s="7">
+        <v>201379</v>
+      </c>
+      <c r="B530" s="7" t="s">
         <v>555</v>
       </c>
       <c r="C530" s="1" t="s">
@@ -8660,10 +9326,10 @@
       </c>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="6">
-        <v>201379</v>
-      </c>
-      <c r="B531" s="6" t="s">
+      <c r="A531" s="7">
+        <v>485210</v>
+      </c>
+      <c r="B531" s="7" t="s">
         <v>556</v>
       </c>
       <c r="C531" s="1" t="s">
@@ -8671,10 +9337,10 @@
       </c>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="6">
-        <v>485210</v>
-      </c>
-      <c r="B532" s="6" t="s">
+      <c r="A532" s="7">
+        <v>171631</v>
+      </c>
+      <c r="B532" s="7" t="s">
         <v>557</v>
       </c>
       <c r="C532" s="1" t="s">
@@ -8682,10 +9348,10 @@
       </c>
     </row>
     <row r="533" spans="1:3">
-      <c r="A533" s="6">
-        <v>171631</v>
-      </c>
-      <c r="B533" s="6" t="s">
+      <c r="A533" s="7">
+        <v>304794</v>
+      </c>
+      <c r="B533" s="7" t="s">
         <v>558</v>
       </c>
       <c r="C533" s="1" t="s">
@@ -8693,183 +9359,310 @@
       </c>
     </row>
     <row r="534" spans="1:3">
-      <c r="A534" s="6">
-        <v>304794</v>
-      </c>
-      <c r="B534" s="6" t="s">
+      <c r="A534" s="7">
+        <v>225018</v>
+      </c>
+      <c r="B534" s="7" t="s">
         <v>559</v>
       </c>
       <c r="C534" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:3">
-      <c r="A535" s="6">
-        <v>225018</v>
-      </c>
-      <c r="B535" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="C535" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="6"/>
-      <c r="B541" s="6"/>
+      <c r="A541" s="7"/>
+      <c r="B541" s="7"/>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="6"/>
-      <c r="B542" s="6"/>
+      <c r="A542" s="7"/>
+      <c r="B542" s="7"/>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="6"/>
-      <c r="B543" s="6"/>
+      <c r="A543" s="7"/>
+      <c r="B543" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B187">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E187">
+    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E188">
+    <cfRule type="duplicateValues" dxfId="1" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="161"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E189">
+    <cfRule type="duplicateValues" dxfId="1" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E190">
+    <cfRule type="duplicateValues" dxfId="1" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B194">
-    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="160"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E194">
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="158"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E195">
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E196">
+    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E197">
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E198">
+    <cfRule type="duplicateValues" dxfId="1" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E225">
+    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E270">
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B289">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E289">
+    <cfRule type="duplicateValues" dxfId="1" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290">
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E290">
+    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="145"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E304">
+    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E310">
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B311">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E311">
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B312">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E312">
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E313">
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E314">
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E315">
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E316">
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E317">
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E318">
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E319">
+    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E321">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E322">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E323">
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B324">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E324">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E325">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F156:F158">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="2" priority="82" operator="notEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="1" operator="between" text="Free">
+    <cfRule type="containsText" dxfId="3" priority="81" operator="between" text="Free">
       <formula>NOT(ISERROR(SEARCH("Free",F156)))</formula>
     </cfRule>
   </conditionalFormatting>
